--- a/testdata/listForExecution.xlsx
+++ b/testdata/listForExecution.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$117</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="241">
   <si>
     <t>TestName</t>
   </si>
@@ -62,18 +62,18 @@
     <t>data</t>
   </si>
   <si>
+    <t>off</t>
+  </si>
+  <si>
+    <t>Product_Summary_Favourite_account_[WEB]</t>
+  </si>
+  <si>
+    <t>C70765</t>
+  </si>
+  <si>
     <t>on</t>
   </si>
   <si>
-    <t>off</t>
-  </si>
-  <si>
-    <t>Product_Summary_Favourite_account_[WEB]</t>
-  </si>
-  <si>
-    <t>C70765</t>
-  </si>
-  <si>
     <t>General-Dashboard-Quick_Links_[WEB]</t>
   </si>
   <si>
@@ -92,13 +92,13 @@
     <t>C70768</t>
   </si>
   <si>
-    <t>Product_Summary-Edit_Product_view-edit_name_of_account_[WEB]_1</t>
+    <t>Product_Summary-Edit_Product_view-edit_name_of_account_[WEB]</t>
   </si>
   <si>
     <t>C70769</t>
   </si>
   <si>
-    <t>Product_Summary-Edit_Product_view-edit_name_of_account-Invalid_[WEB]_1</t>
+    <t>Product_Summary-Edit_Product_view-edit_name_of_account-Invalid_[WEB]</t>
   </si>
   <si>
     <t>C70770</t>
@@ -110,7 +110,7 @@
     <t>C70771</t>
   </si>
   <si>
-    <t>Term_Deposits_Lists_[WEB]</t>
+    <t>Product_Summary-Term_Deposits_Lists_[WEB]</t>
   </si>
   <si>
     <t>C70772</t>
@@ -128,403 +128,631 @@
     <t>C70774</t>
   </si>
   <si>
-    <t>Product_Summary-Hide/Show_account_on_Product_List_[WEB]_1</t>
+    <t>Product_Summary-Hide/Show_Product_on_Product_List_[WEB]_Current_Domestic_Account</t>
   </si>
   <si>
     <t>C70775</t>
   </si>
   <si>
+    <t>Product_Summary-Hide/Show_Product_on_Product_List_[WEB]_Saving_Accounts</t>
+  </si>
+  <si>
+    <t>C70776</t>
+  </si>
+  <si>
+    <t>Product_Summary-Hide/Show_Product_on_Product_List_[WEB]_Loan_Accounts</t>
+  </si>
+  <si>
+    <t>C70777</t>
+  </si>
+  <si>
+    <t>Product_Summary-Hide/Show_Product_on_Product_List_[WEB]_Term_Deposits</t>
+  </si>
+  <si>
+    <t>C70778</t>
+  </si>
+  <si>
+    <t>Product_Summary-Hide/Show_Product_on_Product_List_[WEB]_Current_Foreign_Accounts</t>
+  </si>
+  <si>
+    <t>C70779</t>
+  </si>
+  <si>
     <t>General-Dashboard-Page_overview_[WEB]</t>
   </si>
   <si>
-    <t>C70776</t>
+    <t>C70780</t>
   </si>
   <si>
     <t>Foreign_Current_Account_Product_Details_Account_Details_[WEB]</t>
   </si>
   <si>
-    <t>C70777</t>
+    <t>C70781</t>
   </si>
   <si>
     <t>Current_Accounts-Transactions_Details-Create_Confirmation_[WEB]</t>
   </si>
   <si>
-    <t>C70778</t>
-  </si>
-  <si>
-    <t>Current_Accounts-Transactions_List_select_Currency_[WEB]_2</t>
-  </si>
-  <si>
-    <t>C70779</t>
+    <t>C70782</t>
   </si>
   <si>
     <t>Current_Domestic_Accounts-Transactions-Download_option_[WEB]</t>
   </si>
   <si>
-    <t>C70780</t>
+    <t>C70784</t>
   </si>
   <si>
     <t>Foreign_Current_Accounts-Transactions-Filter_By_Type_[WEB]</t>
   </si>
   <si>
-    <t>C70781</t>
+    <t>C70785</t>
   </si>
   <si>
     <t>Current_Domestic_Account-Transactions-Filter_By_Type_[WEB]</t>
   </si>
   <si>
-    <t>C70782</t>
+    <t>C70786</t>
   </si>
   <si>
     <t>Current_Domestic_Accounts-Transactions-Filter_By_Date-Predefined_Date_Range_[WEB]</t>
   </si>
   <si>
-    <t>C70783</t>
+    <t>C70787</t>
   </si>
   <si>
     <t>Foreign_Current_Accounts-Multiple-Filter_Invalid_[WEB]</t>
   </si>
   <si>
-    <t>C70784</t>
+    <t>C70788</t>
   </si>
   <si>
     <t>Current_Foreign_Accounts-Transactions-Download_option_[WEB]</t>
   </si>
   <si>
-    <t>C70785</t>
+    <t>C70789</t>
   </si>
   <si>
     <t>Current_Domestic_Accounts-Multiple-Filter_Invalid_[WEB]</t>
   </si>
   <si>
-    <t>C70786</t>
+    <t>C70790</t>
   </si>
   <si>
     <t>Foreign_Current_Account-Transactions-Filter_By_Date-Predefined_Date_Range_[WEB]</t>
   </si>
   <si>
-    <t>C70787</t>
+    <t>C70791</t>
   </si>
   <si>
     <t>Manage_Products-Favorite_account_[WEB]</t>
   </si>
   <si>
-    <t>C70788</t>
+    <t>C70792</t>
   </si>
   <si>
     <t>Manage_Products-Favorite_account-Removal_of_the_favorite_account_[WEB]</t>
   </si>
   <si>
-    <t>C70789</t>
+    <t>C70793</t>
   </si>
   <si>
     <t>Manage_Products-Hide/Show_account_on_Product_List_[WEB]_1</t>
   </si>
   <si>
-    <t>C70790</t>
+    <t>C70794</t>
   </si>
   <si>
     <t>Manage_Products-Hide/Show_account_on_Product_List_Invalid[WEB]_1</t>
   </si>
   <si>
-    <t>C70791</t>
+    <t>C70795</t>
   </si>
   <si>
     <t>Manage_Products-Nickname_Product_Returning_To_Default_Name_[WEB]</t>
   </si>
   <si>
-    <t>C70792</t>
+    <t>C70796</t>
   </si>
   <si>
     <t>Manage_Products-Nickname_Product_[WEB]_Invalid</t>
   </si>
   <si>
-    <t>C70793</t>
+    <t>C70797</t>
   </si>
   <si>
     <t>Manage_Products-Nickname_Product_[WEB]</t>
   </si>
   <si>
-    <t>C70794</t>
+    <t>C70798</t>
   </si>
   <si>
     <t>Products_Current_Accounts-Cheques_[WEB]</t>
   </si>
   <si>
-    <t>C70795</t>
+    <t>C70799</t>
   </si>
   <si>
     <t>Products_Current_Accounts-Cheques-Filter_[WEB]</t>
   </si>
   <si>
-    <t>C70796</t>
+    <t>C70800</t>
   </si>
   <si>
     <t>Products_Current_Accounts-Cheques-Input_Fields-invalid_[WEB]</t>
   </si>
   <si>
-    <t>C70797</t>
+    <t>C70801</t>
   </si>
   <si>
     <t>Current_Domestic_Accounts-Transactions_List_[WEB]</t>
   </si>
   <si>
-    <t>C70798</t>
+    <t>C70802</t>
   </si>
   <si>
     <t>Current_Foreign_Accounts-Transactions_List_[WEB]</t>
   </si>
   <si>
-    <t>C70799</t>
+    <t>C70803</t>
   </si>
   <si>
     <t>Foreign_Current_Accounts-Transactions_List_select_Currency_[WEB]</t>
   </si>
   <si>
-    <t>C70800</t>
+    <t>C70804</t>
   </si>
   <si>
     <t>Current_Domestic_Accounts-Details-Financial_Details_[WEB]</t>
   </si>
   <si>
-    <t>C70801</t>
+    <t>C70805</t>
   </si>
   <si>
     <t>Credit_Cards-Header_Display_[WEB]</t>
   </si>
   <si>
-    <t>C70802</t>
+    <t>C70806</t>
   </si>
   <si>
     <t>Current_Domestic_Accounts-Transactions_List_No_Transactions_[WEB]</t>
   </si>
   <si>
-    <t>C70803</t>
+    <t>C70807</t>
   </si>
   <si>
     <t>Current_Domestic_Accounts-Transactions_Filter_By_Date-Date_Picker_[WEB]</t>
   </si>
   <si>
-    <t>C70804</t>
+    <t>C70808</t>
   </si>
   <si>
     <t>Current_Domestic_Accounts-Transactions-Filter_By_Amount_[WEB]</t>
   </si>
   <si>
-    <t>C70805</t>
+    <t>C70809</t>
   </si>
   <si>
     <t>Current_Domestic_Accounts-Transactions-Filter_By_Amount_Invalid_[WEB]</t>
   </si>
   <si>
-    <t>C70806</t>
+    <t>C70810</t>
   </si>
   <si>
     <t>Current_Foreign_Accounts_Product_Details_Financial_Details_Is_Not_Visible_[WEB]</t>
   </si>
   <si>
-    <t>C70807</t>
+    <t>C70811</t>
   </si>
   <si>
     <t>Current_Foreign_Accounts-Transactions_List_No_Transactions_[WEB]</t>
   </si>
   <si>
-    <t>C70808</t>
+    <t>C70812</t>
   </si>
   <si>
     <t>Current_Foreign_Accounts-Transactions_Filter_By_Date-Date_Picker_[WEB]</t>
   </si>
   <si>
-    <t>C70809</t>
+    <t>C70813</t>
   </si>
   <si>
     <t>Current_Foreign_Accounts-Transactions-Filter_By_Amount_[WEB]</t>
   </si>
   <si>
-    <t>C70810</t>
+    <t>C70814</t>
   </si>
   <si>
     <t>Current_Foreign_Accounts-Transactions-Filter_By_Amount_Invalid_[WEB]</t>
   </si>
   <si>
-    <t>C70811</t>
+    <t>C70815</t>
   </si>
   <si>
     <t>Savings_Accounts_Details-Financial_Details_[WEB]</t>
   </si>
   <si>
-    <t>C70812</t>
+    <t>C70816</t>
   </si>
   <si>
     <t>Savings_Accounts_Details-Account_Details_[WEB]</t>
   </si>
   <si>
-    <t>C70813</t>
+    <t>C70817</t>
   </si>
   <si>
     <t>Credit_Cards-Transactions_Filter_By_Date-Date_Picker_[WEB]</t>
   </si>
   <si>
-    <t>C70814</t>
+    <t>C70818</t>
   </si>
   <si>
     <t>Credit_Cards-Transactions_Filter_By_Date-Date_Picker-invalid_[WEB]</t>
   </si>
   <si>
-    <t>C70815</t>
+    <t>C70819</t>
   </si>
   <si>
     <t>Credit_Cards-Transactions_List_No_Transactions_[WEB]</t>
   </si>
   <si>
-    <t>C70816</t>
+    <t>C70820</t>
   </si>
   <si>
     <t>Term_Deposits-Details_Account_Details_[WEB]</t>
   </si>
   <si>
-    <t>C70817</t>
+    <t>C70821</t>
   </si>
   <si>
     <t>Product_Summary-Current_Foreign_Accounts_List_[WEB]</t>
   </si>
   <si>
-    <t>C70818</t>
-  </si>
-  <si>
-    <t>Product_Summary-Savings_Accounts_List_Domestic_[WEB]</t>
-  </si>
-  <si>
-    <t>C70819</t>
+    <t>C70822</t>
+  </si>
+  <si>
+    <t>Product_Summary-Savings_Accounts_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70823</t>
   </si>
   <si>
     <t>Current_Domestic_Accounts-Transactions_Filter-Invalid_[WEB]</t>
   </si>
   <si>
-    <t>C70820</t>
+    <t>C70824</t>
   </si>
   <si>
     <t>Current_Foreign_Accounts-Transactions_Filter-Invalid_[WEB]</t>
   </si>
   <si>
-    <t>C70821</t>
+    <t>C70825</t>
   </si>
   <si>
     <t>Payments_Recipient-Save_Recipient_[WEB]</t>
   </si>
   <si>
-    <t>C70822</t>
+    <t>C70826</t>
   </si>
   <si>
     <t>Payments_Recipient-Delete_Recipient_[WEB]</t>
   </si>
   <si>
-    <t>C70823</t>
+    <t>C70827</t>
   </si>
   <si>
     <t>Payments_Recipient-Update_Recipient_[WEB]</t>
   </si>
   <si>
-    <t>C70824</t>
+    <t>C70828</t>
   </si>
   <si>
     <t>Payments_Recipient-Edit_Recipient-Invalid_[WEB]</t>
   </si>
   <si>
-    <t>C70825</t>
+    <t>C70829</t>
   </si>
   <si>
     <t>Term_Deposits-Accounts_Details[WEB]</t>
   </si>
   <si>
-    <t>C70826</t>
+    <t>C70830</t>
   </si>
   <si>
     <t>Product_Summary-Loan_List[WEB]</t>
   </si>
   <si>
-    <t>C70827</t>
+    <t>C70831</t>
   </si>
   <si>
     <t>Foreign_Current_Accounts-Transactions-Search_[WEB]</t>
   </si>
   <si>
+    <t>C70832</t>
+  </si>
+  <si>
     <t>Current_Domestic_Accounts-Transactions-Search_[WEB]</t>
   </si>
   <si>
+    <t>C70833</t>
+  </si>
+  <si>
     <t>Payments_Recipient-Edit_Recipient-Edit_Account_number-invalid_[WEB]</t>
   </si>
   <si>
-    <t>C70828</t>
+    <t>C70834</t>
   </si>
   <si>
     <t>Payments_Recipient-Update_Recipient-Update_Account_number_[WEB]</t>
   </si>
   <si>
-    <t>C70829</t>
+    <t>C70835</t>
   </si>
   <si>
     <t>Payments-Domestic_Payments-Cancel_Button_[WEB]</t>
   </si>
   <si>
+    <t>C70836</t>
+  </si>
+  <si>
     <t>Credit_Cards-Transactions-Download_Option_[WEB]</t>
   </si>
   <si>
+    <t>C70837</t>
+  </si>
+  <si>
     <t>Payments-Domestic_Payments-Back_Button_[WEB]</t>
   </si>
   <si>
+    <t>C70838</t>
+  </si>
+  <si>
     <t>Credit_Cards-Transactions_Filter_By_Type_[WEB]</t>
   </si>
   <si>
-    <t>C70830</t>
+    <t>C70839</t>
   </si>
   <si>
     <t>Credit_Cards-Transactions_Filter_By_Amount_[WEB]</t>
   </si>
   <si>
-    <t>C70831</t>
+    <t>C70840</t>
   </si>
   <si>
     <t>Credit_Cards-Transactions_Filter_By_Amount_invalid_[WEB]</t>
   </si>
   <si>
+    <t>C70841</t>
+  </si>
+  <si>
     <t>Payments_Payments_Overview_Display_Options_For_The_Selected_Account_[WEB]</t>
   </si>
   <si>
-    <t>C70832</t>
+    <t>C70842</t>
   </si>
   <si>
     <t>Credit_Cards-Transactions-Filter-Filter_By_Status_[WEB]</t>
   </si>
   <si>
+    <t>C70843</t>
+  </si>
+  <si>
     <t>Credit_Cards-Transactions_Details[WEB]</t>
   </si>
   <si>
-    <t>C70833</t>
+    <t>C70844</t>
   </si>
   <si>
     <t>Domestic_Payments_Modify_Data_[WEB]</t>
   </si>
   <si>
-    <t>C70834</t>
+    <t>C70845</t>
   </si>
   <si>
     <t>Domestic_Payments_In_Future_[WEB]</t>
   </si>
   <si>
-    <t>C70835</t>
+    <t>C70846</t>
   </si>
   <si>
     <t>Credit_Cards-Transactions-Filter_Multiple_Filter_Invalid_[WEB]</t>
   </si>
   <si>
-    <t>C70836</t>
+    <t>C70847</t>
   </si>
   <si>
     <t>Payments-Domestic_Payments-Create_New_Recipient_[WEB]</t>
   </si>
   <si>
-    <t>C70837</t>
+    <t>C70848</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-Flow_Disruption_Cancel-Back_[WEB]</t>
+  </si>
+  <si>
+    <t>C70849</t>
+  </si>
+  <si>
+    <t>C70850</t>
+  </si>
+  <si>
+    <t>Payments-Payments_Archive-Filter_Payments_By_Date_[WEB]</t>
+  </si>
+  <si>
+    <t>C70851</t>
+  </si>
+  <si>
+    <t>Payments_Payments_Archive_Filter_Payments_By_Amount-Invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70852</t>
+  </si>
+  <si>
+    <t>Payments_Payments_Archive_Filter_Payments_By_Status_[WEB]</t>
+  </si>
+  <si>
+    <t>C70853</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70854</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Header_[WEB]</t>
+  </si>
+  <si>
+    <t>C70855</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-From_Savings_Account_RSD_[WEB]-To_Savings_Account</t>
+  </si>
+  <si>
+    <t>C70856</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-From_Savings_Account_RSD_[WEB]-To_Current_Account</t>
+  </si>
+  <si>
+    <t>C70857</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-From_Savings_Account_RSD_[WEB]-To_Charge_Card</t>
+  </si>
+  <si>
+    <t>C70858</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-From_Current_Account_RSD_[WEB]-To_Current_Account</t>
+  </si>
+  <si>
+    <t>C70859</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-From_Current_Account_RSD_[WEB]-To_Savings_Account</t>
+  </si>
+  <si>
+    <t>C70860</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-From_Current_Account_RSD_[WEB]-To_Charge_Card</t>
+  </si>
+  <si>
+    <t>C70861</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-Invalid_Account_Combination_[WEB]</t>
+  </si>
+  <si>
+    <t>C70862</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Annuity_Plan_[WEB]</t>
+  </si>
+  <si>
+    <t>C70863</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Annuity_Plan-Filter_[WEB]</t>
+  </si>
+  <si>
+    <t>C70864</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Payments_[WEB]</t>
+  </si>
+  <si>
+    <t>C70865</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Payments-Filter_[WEB]</t>
+  </si>
+  <si>
+    <t>C70866</t>
+  </si>
+  <si>
+    <t>Term_Deposits-Details-Financial_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70867</t>
+  </si>
+  <si>
+    <t>Payments_Payments_Archive-Create_Confirmation_[WEB]</t>
+  </si>
+  <si>
+    <t>C70868</t>
+  </si>
+  <si>
+    <t>Authentication-Web_Login-Logout_[WEB]</t>
+  </si>
+  <si>
+    <t>C70869</t>
+  </si>
+  <si>
+    <t>Authentication-Web_Login-Login_With_OTP_[WEB]</t>
+  </si>
+  <si>
+    <t>C70870</t>
+  </si>
+  <si>
+    <t>Product_Summary-Current_Domestic_Accounts_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70871</t>
+  </si>
+  <si>
+    <t>Product_Summary-Term_Deposits_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70872</t>
+  </si>
+  <si>
+    <t>General-Login_Page_Elements-Overview_PreLogin_Page_[WEB]</t>
+  </si>
+  <si>
+    <t>C70873</t>
+  </si>
+  <si>
+    <t>General-Login_Page_Elements-Links_[WEB]</t>
+  </si>
+  <si>
+    <t>C70874</t>
+  </si>
+  <si>
+    <t>Authentication-Web_Login-Login_With_OTP-Invalid_OTP_[WEB]</t>
+  </si>
+  <si>
+    <t>C70875</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Annuity_Plan-Filter-invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70876</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Payments-Filter-invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70877</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments_[WEB]</t>
+  </si>
+  <si>
+    <t>C70878</t>
+  </si>
+  <si>
+    <t>Payments-Domestic_Payments-Confirmation_[WEB]</t>
+  </si>
+  <si>
+    <t>C70879</t>
+  </si>
+  <si>
+    <t>Payments-Payments_Overview_[WEB]</t>
+  </si>
+  <si>
+    <t>C70880</t>
   </si>
 </sst>
 </file>
@@ -1149,13 +1377,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1488,7 +1715,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F117"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="91.1388888888889" customWidth="1"/>
@@ -1527,31 +1754,31 @@
       <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>10</v>
+      <c r="E3" t="s">
+        <v>13</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1567,11 +1794,11 @@
       <c r="D4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1587,11 +1814,11 @@
       <c r="D5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1607,11 +1834,11 @@
       <c r="D6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1627,11 +1854,11 @@
       <c r="D7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>10</v>
+      <c r="E7" t="s">
+        <v>13</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1647,11 +1874,11 @@
       <c r="D8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>10</v>
+      <c r="E8" t="s">
+        <v>13</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1667,11 +1894,11 @@
       <c r="D9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1687,11 +1914,11 @@
       <c r="D10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" t="s">
         <v>10</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1707,11 +1934,11 @@
       <c r="D11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1727,11 +1954,11 @@
       <c r="D12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>10</v>
+      <c r="E12" t="s">
+        <v>13</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1747,11 +1974,11 @@
       <c r="D13" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>10</v>
+      <c r="E13" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1767,11 +1994,11 @@
       <c r="D14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>10</v>
+      <c r="E14" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1787,11 +2014,11 @@
       <c r="D15" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>10</v>
+      <c r="E15" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1807,11 +2034,11 @@
       <c r="D16" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>10</v>
+      <c r="E16" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1827,11 +2054,11 @@
       <c r="D17" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>10</v>
+      <c r="E17" t="s">
+        <v>13</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1847,15 +2074,15 @@
       <c r="D18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" t="s">
         <v>10</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="4" t="s">
+      <c r="A19" t="s">
         <v>44</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -1867,11 +2094,11 @@
       <c r="D19" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" t="s">
         <v>10</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1887,11 +2114,11 @@
       <c r="D20" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" t="s">
         <v>10</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1907,15 +2134,15 @@
       <c r="D21" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" t="s">
         <v>10</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" t="s">
+      <c r="A22" s="3" t="s">
         <v>50</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -1927,11 +2154,11 @@
       <c r="D22" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>10</v>
+      <c r="E22" t="s">
+        <v>13</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1947,15 +2174,15 @@
       <c r="D23" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>10</v>
+      <c r="E23" t="s">
+        <v>13</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="4" t="s">
+      <c r="A24" t="s">
         <v>54</v>
       </c>
       <c r="B24" s="2" t="s">
@@ -1967,11 +2194,11 @@
       <c r="D24" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="E24" t="s">
         <v>10</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1987,11 +2214,11 @@
       <c r="D25" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" t="s">
         <v>10</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -2007,15 +2234,15 @@
       <c r="D26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" t="s">
         <v>10</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" t="s">
+      <c r="A27" s="3" t="s">
         <v>60</v>
       </c>
       <c r="B27" s="2" t="s">
@@ -2027,11 +2254,11 @@
       <c r="D27" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="E27" t="s">
         <v>10</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -2047,11 +2274,11 @@
       <c r="D28" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" t="s">
         <v>10</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -2067,11 +2294,11 @@
       <c r="D29" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" t="s">
         <v>10</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -2087,11 +2314,11 @@
       <c r="D30" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" t="s">
         <v>10</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -2107,11 +2334,11 @@
       <c r="D31" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="E31" t="s">
         <v>10</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -2127,11 +2354,11 @@
       <c r="D32" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E32" t="s">
         <v>10</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -2147,11 +2374,11 @@
       <c r="D33" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" t="s">
         <v>10</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -2167,11 +2394,11 @@
       <c r="D34" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E34" t="s">
         <v>10</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -2187,11 +2414,11 @@
       <c r="D35" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E35" t="s">
         <v>10</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -2207,11 +2434,11 @@
       <c r="D36" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E36" t="s">
         <v>10</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -2227,11 +2454,11 @@
       <c r="D37" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" t="s">
         <v>10</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -2247,11 +2474,11 @@
       <c r="D38" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" t="s">
         <v>10</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -2267,11 +2494,11 @@
       <c r="D39" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="E39" t="s">
         <v>10</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -2287,11 +2514,11 @@
       <c r="D40" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E40" s="3" t="s">
-        <v>10</v>
+      <c r="E40" t="s">
+        <v>13</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -2307,11 +2534,11 @@
       <c r="D41" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>10</v>
+      <c r="E41" t="s">
+        <v>13</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -2327,11 +2554,11 @@
       <c r="D42" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="E42" t="s">
         <v>10</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -2347,11 +2574,11 @@
       <c r="D43" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="E43" t="s">
         <v>10</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -2367,11 +2594,11 @@
       <c r="D44" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="E44" t="s">
         <v>10</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -2387,11 +2614,11 @@
       <c r="D45" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>10</v>
+      <c r="E45" t="s">
+        <v>13</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -2407,11 +2634,11 @@
       <c r="D46" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E46" s="3" t="s">
-        <v>10</v>
+      <c r="E46" t="s">
+        <v>13</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -2427,11 +2654,11 @@
       <c r="D47" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="E47" t="s">
         <v>10</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -2447,11 +2674,11 @@
       <c r="D48" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>10</v>
+      <c r="E48" t="s">
+        <v>13</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -2467,11 +2694,11 @@
       <c r="D49" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>10</v>
+      <c r="E49" t="s">
+        <v>13</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2487,11 +2714,11 @@
       <c r="D50" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E50" s="3" t="s">
+      <c r="E50" t="s">
         <v>10</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -2507,11 +2734,11 @@
       <c r="D51" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E51" s="3" t="s">
-        <v>10</v>
+      <c r="E51" t="s">
+        <v>13</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -2527,11 +2754,11 @@
       <c r="D52" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>10</v>
+      <c r="E52" t="s">
+        <v>13</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -2547,11 +2774,11 @@
       <c r="D53" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E53" s="3" t="s">
-        <v>10</v>
+      <c r="E53" t="s">
+        <v>13</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -2567,11 +2794,11 @@
       <c r="D54" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E54" s="3" t="s">
-        <v>10</v>
+      <c r="E54" t="s">
+        <v>13</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -2587,11 +2814,11 @@
       <c r="D55" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E55" s="3" t="s">
+      <c r="E55" t="s">
         <v>10</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -2607,11 +2834,11 @@
       <c r="D56" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E56" s="3" t="s">
+      <c r="E56" t="s">
         <v>10</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -2627,11 +2854,11 @@
       <c r="D57" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="E57" t="s">
         <v>10</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -2647,11 +2874,11 @@
       <c r="D58" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>10</v>
+      <c r="E58" t="s">
+        <v>13</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -2667,11 +2894,11 @@
       <c r="D59" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>10</v>
+      <c r="E59" t="s">
+        <v>13</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -2687,11 +2914,11 @@
       <c r="D60" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E60" s="3" t="s">
-        <v>10</v>
+      <c r="E60" t="s">
+        <v>13</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2707,11 +2934,11 @@
       <c r="D61" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E61" s="3" t="s">
-        <v>10</v>
+      <c r="E61" t="s">
+        <v>13</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -2727,11 +2954,11 @@
       <c r="D62" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>10</v>
+      <c r="E62" t="s">
+        <v>13</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -2747,11 +2974,11 @@
       <c r="D63" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E63" s="3" t="s">
+      <c r="E63" t="s">
         <v>10</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -2767,11 +2994,11 @@
       <c r="D64" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E64" s="3" t="s">
+      <c r="E64" t="s">
         <v>10</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -2787,11 +3014,11 @@
       <c r="D65" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E65" s="3" t="s">
+      <c r="E65" t="s">
         <v>10</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -2799,7 +3026,7 @@
         <v>138</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>8</v>
@@ -2807,19 +3034,19 @@
       <c r="D66" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E66" s="3" t="s">
+      <c r="E66" t="s">
         <v>10</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>8</v>
@@ -2827,19 +3054,19 @@
       <c r="D67" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E67" s="3" t="s">
-        <v>10</v>
+      <c r="E67" t="s">
+        <v>13</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="4" t="s">
-        <v>140</v>
+      <c r="A68" t="s">
+        <v>142</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>8</v>
@@ -2847,19 +3074,19 @@
       <c r="D68" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E68" s="3" t="s">
+      <c r="E68" t="s">
         <v>10</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:6">
-      <c r="A69" s="4" t="s">
-        <v>142</v>
+      <c r="A69" t="s">
+        <v>144</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>8</v>
@@ -2867,19 +3094,19 @@
       <c r="D69" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E69" s="3" t="s">
+      <c r="E69" t="s">
         <v>10</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="70" spans="1:6">
-      <c r="A70" s="4" t="s">
-        <v>144</v>
+      <c r="A70" t="s">
+        <v>146</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>8</v>
@@ -2887,19 +3114,19 @@
       <c r="D70" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E70" s="3" t="s">
+      <c r="E70" t="s">
         <v>10</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:6">
-      <c r="A71" s="4" t="s">
-        <v>145</v>
+      <c r="A71" s="3" t="s">
+        <v>148</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>8</v>
@@ -2907,19 +3134,19 @@
       <c r="D71" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E71" s="3" t="s">
+      <c r="E71" t="s">
         <v>10</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72" spans="1:6">
-      <c r="A72" s="4" t="s">
-        <v>146</v>
+      <c r="A72" s="3" t="s">
+        <v>150</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>8</v>
@@ -2927,19 +3154,19 @@
       <c r="D72" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E72" s="3" t="s">
+      <c r="E72" t="s">
         <v>10</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="73" spans="1:6">
-      <c r="A73" t="s">
-        <v>147</v>
+      <c r="A73" s="3" t="s">
+        <v>152</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>8</v>
@@ -2947,19 +3174,19 @@
       <c r="D73" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E73" s="3" t="s">
-        <v>10</v>
+      <c r="E73" t="s">
+        <v>13</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="74" spans="1:6">
-      <c r="A74" t="s">
-        <v>149</v>
+      <c r="A74" s="3" t="s">
+        <v>154</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>8</v>
@@ -2967,19 +3194,19 @@
       <c r="D74" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E74" s="3" t="s">
+      <c r="E74" t="s">
         <v>10</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:6">
-      <c r="A75" t="s">
-        <v>151</v>
+      <c r="A75" s="3" t="s">
+        <v>156</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>8</v>
@@ -2987,19 +3214,19 @@
       <c r="D75" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E75" s="3" t="s">
-        <v>10</v>
+      <c r="E75" t="s">
+        <v>13</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>8</v>
@@ -3007,19 +3234,19 @@
       <c r="D76" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E76" s="3" t="s">
+      <c r="E76" t="s">
         <v>10</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>8</v>
@@ -3027,19 +3254,19 @@
       <c r="D77" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E77" s="3" t="s">
+      <c r="E77" t="s">
         <v>10</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>8</v>
@@ -3047,19 +3274,19 @@
       <c r="D78" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E78" s="3" t="s">
+      <c r="E78" t="s">
         <v>10</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>8</v>
@@ -3067,19 +3294,19 @@
       <c r="D79" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E79" s="3" t="s">
+      <c r="E79" t="s">
         <v>10</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>8</v>
@@ -3087,19 +3314,19 @@
       <c r="D80" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E80" s="3" t="s">
+      <c r="E80" t="s">
         <v>10</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>8</v>
@@ -3107,19 +3334,19 @@
       <c r="D81" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E81" s="3" t="s">
+      <c r="E81" t="s">
         <v>10</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>8</v>
@@ -3127,74 +3354,750 @@
       <c r="D82" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E82" s="3" t="s">
-        <v>10</v>
+      <c r="E82" t="s">
+        <v>13</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" t="s">
+        <v>172</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E83" t="s">
+        <v>13</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" t="s">
+        <v>174</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E84" t="s">
+        <v>10</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" t="s">
+        <v>176</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E85" t="s">
+        <v>13</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86" t="s">
+        <v>178</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E86" t="s">
+        <v>13</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87" t="s">
+        <v>166</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E87" t="s">
+        <v>10</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88" t="s">
+        <v>181</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E88" t="s">
+        <v>10</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89" t="s">
+        <v>183</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E89" t="s">
+        <v>10</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" t="s">
+        <v>185</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E90" t="s">
+        <v>10</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91" t="s">
+        <v>187</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E91" t="s">
+        <v>10</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" t="s">
+        <v>189</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E92" t="s">
+        <v>10</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93" t="s">
+        <v>191</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E93" t="s">
+        <v>10</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94" t="s">
+        <v>193</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E94" t="s">
+        <v>10</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95" t="s">
+        <v>195</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E95" t="s">
+        <v>10</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" t="s">
+        <v>197</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E96" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" t="s">
+        <v>199</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E97" t="s">
+        <v>13</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" t="s">
+        <v>201</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E98" t="s">
+        <v>13</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" t="s">
+        <v>203</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E99" t="s">
+        <v>10</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100" t="s">
+        <v>205</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E100" t="s">
+        <v>13</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101" t="s">
+        <v>207</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E101" t="s">
+        <v>13</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102" t="s">
+        <v>209</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E102" t="s">
+        <v>13</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="A103" t="s">
+        <v>211</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E103" t="s">
+        <v>13</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
+      <c r="A104" t="s">
+        <v>213</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E104" t="s">
+        <v>13</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105" t="s">
+        <v>215</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E105" t="s">
+        <v>10</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106" t="s">
+        <v>217</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E106" t="s">
+        <v>13</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107" t="s">
+        <v>219</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E107" t="s">
+        <v>13</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108" t="s">
+        <v>221</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E108" t="s">
+        <v>13</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109" t="s">
+        <v>223</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E109" t="s">
+        <v>13</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110" t="s">
+        <v>225</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E110" t="s">
+        <v>13</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111" t="s">
+        <v>227</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E111" t="s">
+        <v>13</v>
+      </c>
+      <c r="F111" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112" t="s">
+        <v>229</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E112" t="s">
+        <v>13</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113" t="s">
+        <v>231</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E113" t="s">
+        <v>13</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="A114" t="s">
+        <v>233</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E114" t="s">
+        <v>13</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
+      <c r="A115" t="s">
+        <v>235</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E115" t="s">
+        <v>13</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="A116" t="s">
+        <v>237</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E116" t="s">
+        <v>13</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
+      <c r="A117" t="s">
+        <v>239</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E117" t="s">
+        <v>10</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F81" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F117" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
-  <conditionalFormatting sqref="A32">
-    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+  <conditionalFormatting sqref="A35">
+    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A66">
+  <conditionalFormatting sqref="A69">
     <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B66">
+  <conditionalFormatting sqref="A74">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A75">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A80">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A70:A71">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
     <cfRule type="duplicateValues" dxfId="0" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B70">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A71">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A72">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A77">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A67:A68">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A75:A76">
+  <conditionalFormatting sqref="A78:A79">
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B52:B65">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B67:B69">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B72:B74">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B75:B76">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  <conditionalFormatting sqref="B$1:B$1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B77:B82">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A65 A69:A70 A73:A74 A78:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B51 B83:B1048576">
+  <conditionalFormatting sqref="A1:A68 A81:A1048576 A76:A77 A72:A73">
     <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/testdata/listForExecution.xlsx
+++ b/testdata/listForExecution.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="28800" windowHeight="12240"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="243">
   <si>
     <t>TestName</t>
   </si>
@@ -753,6 +753,12 @@
   </si>
   <si>
     <t>C70880</t>
+  </si>
+  <si>
+    <t>Product_Summary-Hide/Show_Product_on_Product_List_[WEB]_Credit_Cards</t>
+  </si>
+  <si>
+    <t>C70881</t>
   </si>
 </sst>
 </file>
@@ -1397,7 +1403,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1715,7 +1721,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F117"/>
+  <dimension ref="A1:F118"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="91.1388888888889" customWidth="1"/>
@@ -4055,9 +4061,29 @@
         <v>9</v>
       </c>
       <c r="E117" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F117" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="A118" t="s">
+        <v>241</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E118" t="s">
+        <v>13</v>
+      </c>
+      <c r="F118" s="1" t="s">
         <v>10</v>
       </c>
     </row>

--- a/testdata/listForExecution.xlsx
+++ b/testdata/listForExecution.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12240"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$118</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="243">
   <si>
     <t>TestName</t>
   </si>
@@ -62,6 +62,9 @@
     <t>data</t>
   </si>
   <si>
+    <t>on</t>
+  </si>
+  <si>
     <t>off</t>
   </si>
   <si>
@@ -71,9 +74,6 @@
     <t>C70765</t>
   </si>
   <si>
-    <t>on</t>
-  </si>
-  <si>
     <t>General-Dashboard-Quick_Links_[WEB]</t>
   </si>
   <si>
@@ -104,7 +104,7 @@
     <t>C70770</t>
   </si>
   <si>
-    <t>Product_Summary-Credit_Card_List_[WEB]_1</t>
+    <t>Product_Summary-Credit_Card_List_[WEB]</t>
   </si>
   <si>
     <t>C70771</t>
@@ -1721,13 +1721,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F118"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <dimension ref="A1:G118"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="91.1388888888889" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1747,7 +1747,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:6">
+    <row r="2" s="1" customFormat="1" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -1764,15 +1764,18 @@
         <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>8</v>
@@ -1781,13 +1784,13 @@
         <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1804,10 +1807,13 @@
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1824,10 +1830,13 @@
         <v>10</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -1844,10 +1853,13 @@
         <v>10</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -1861,13 +1873,13 @@
         <v>9</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -1881,13 +1893,13 @@
         <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -1903,11 +1915,14 @@
       <c r="E9" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -1923,11 +1938,14 @@
       <c r="E10" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -1943,11 +1961,14 @@
       <c r="E11" t="s">
         <v>10</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -1961,13 +1982,13 @@
         <v>9</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -1980,14 +2001,14 @@
       <c r="D13" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>13</v>
+      <c r="E13" t="s">
+        <v>10</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -2000,14 +2021,14 @@
       <c r="D14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>13</v>
+      <c r="E14" t="s">
+        <v>10</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -2020,14 +2041,14 @@
       <c r="D15" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>13</v>
+      <c r="E15" t="s">
+        <v>10</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -2040,14 +2061,14 @@
       <c r="D16" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>13</v>
+      <c r="E16" t="s">
+        <v>10</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -2061,13 +2082,13 @@
         <v>9</v>
       </c>
       <c r="E17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -2083,11 +2104,14 @@
       <c r="E18" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -2103,11 +2127,14 @@
       <c r="E19" t="s">
         <v>10</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="F19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -2123,11 +2150,14 @@
       <c r="E20" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="F20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -2143,11 +2173,14 @@
       <c r="E21" t="s">
         <v>10</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="F21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="3" t="s">
         <v>50</v>
       </c>
@@ -2161,13 +2194,13 @@
         <v>9</v>
       </c>
       <c r="E22" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>52</v>
       </c>
@@ -2181,13 +2214,13 @@
         <v>9</v>
       </c>
       <c r="E23" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -2204,10 +2237,13 @@
         <v>10</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G24" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -2224,10 +2260,13 @@
         <v>10</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G25" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -2244,10 +2283,13 @@
         <v>10</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G26" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27" s="3" t="s">
         <v>60</v>
       </c>
@@ -2264,10 +2306,13 @@
         <v>10</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28" t="s">
         <v>62</v>
       </c>
@@ -2284,10 +2329,13 @@
         <v>10</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29" t="s">
         <v>64</v>
       </c>
@@ -2304,10 +2352,13 @@
         <v>10</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G29" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -2324,10 +2375,13 @@
         <v>10</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G30" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31" t="s">
         <v>68</v>
       </c>
@@ -2344,10 +2398,13 @@
         <v>10</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32" t="s">
         <v>70</v>
       </c>
@@ -2364,10 +2421,13 @@
         <v>10</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G32" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>72</v>
       </c>
@@ -2384,10 +2444,13 @@
         <v>10</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>74</v>
       </c>
@@ -2404,10 +2467,13 @@
         <v>10</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G34" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>76</v>
       </c>
@@ -2424,10 +2490,13 @@
         <v>10</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>78</v>
       </c>
@@ -2444,10 +2513,13 @@
         <v>10</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G36" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>80</v>
       </c>
@@ -2464,10 +2536,13 @@
         <v>10</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G37" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>82</v>
       </c>
@@ -2484,10 +2559,13 @@
         <v>10</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G38" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>84</v>
       </c>
@@ -2504,10 +2582,13 @@
         <v>10</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G39" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>86</v>
       </c>
@@ -2521,13 +2602,13 @@
         <v>9</v>
       </c>
       <c r="E40" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>88</v>
       </c>
@@ -2541,13 +2622,13 @@
         <v>9</v>
       </c>
       <c r="E41" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
         <v>90</v>
       </c>
@@ -2563,11 +2644,14 @@
       <c r="E42" t="s">
         <v>10</v>
       </c>
-      <c r="F42" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+      <c r="F42" t="s">
+        <v>11</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>92</v>
       </c>
@@ -2583,11 +2667,14 @@
       <c r="E43" t="s">
         <v>10</v>
       </c>
-      <c r="F43" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="F43" t="s">
+        <v>11</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>94</v>
       </c>
@@ -2603,11 +2690,14 @@
       <c r="E44" t="s">
         <v>10</v>
       </c>
-      <c r="F44" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+      <c r="F44" t="s">
+        <v>11</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>96</v>
       </c>
@@ -2621,13 +2711,13 @@
         <v>9</v>
       </c>
       <c r="E45" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>98</v>
       </c>
@@ -2641,13 +2731,13 @@
         <v>9</v>
       </c>
       <c r="E46" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>100</v>
       </c>
@@ -2664,10 +2754,13 @@
         <v>10</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G47" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>102</v>
       </c>
@@ -2681,13 +2774,13 @@
         <v>9</v>
       </c>
       <c r="E48" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49" t="s">
         <v>104</v>
       </c>
@@ -2701,13 +2794,13 @@
         <v>9</v>
       </c>
       <c r="E49" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50" t="s">
         <v>106</v>
       </c>
@@ -2724,10 +2817,13 @@
         <v>10</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G50" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51" t="s">
         <v>108</v>
       </c>
@@ -2741,13 +2837,13 @@
         <v>9</v>
       </c>
       <c r="E51" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52" t="s">
         <v>110</v>
       </c>
@@ -2761,13 +2857,13 @@
         <v>9</v>
       </c>
       <c r="E52" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
       <c r="A53" t="s">
         <v>112</v>
       </c>
@@ -2781,13 +2877,13 @@
         <v>9</v>
       </c>
       <c r="E53" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54" t="s">
         <v>114</v>
       </c>
@@ -2801,13 +2897,13 @@
         <v>9</v>
       </c>
       <c r="E54" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55" t="s">
         <v>116</v>
       </c>
@@ -2824,10 +2920,13 @@
         <v>10</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G55" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
       <c r="A56" t="s">
         <v>118</v>
       </c>
@@ -2844,10 +2943,13 @@
         <v>10</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G56" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
       <c r="A57" t="s">
         <v>120</v>
       </c>
@@ -2864,10 +2966,13 @@
         <v>10</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G57" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
       <c r="A58" t="s">
         <v>122</v>
       </c>
@@ -2881,13 +2986,13 @@
         <v>9</v>
       </c>
       <c r="E58" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
       <c r="A59" t="s">
         <v>124</v>
       </c>
@@ -2901,13 +3006,13 @@
         <v>9</v>
       </c>
       <c r="E59" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
       <c r="A60" t="s">
         <v>126</v>
       </c>
@@ -2921,13 +3026,13 @@
         <v>9</v>
       </c>
       <c r="E60" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
       <c r="A61" t="s">
         <v>128</v>
       </c>
@@ -2941,13 +3046,13 @@
         <v>9</v>
       </c>
       <c r="E61" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
       <c r="A62" t="s">
         <v>130</v>
       </c>
@@ -2961,13 +3066,13 @@
         <v>9</v>
       </c>
       <c r="E62" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
       <c r="A63" t="s">
         <v>132</v>
       </c>
@@ -2984,10 +3089,13 @@
         <v>10</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G63" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
       <c r="A64" t="s">
         <v>134</v>
       </c>
@@ -3004,10 +3112,13 @@
         <v>10</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G64" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
       <c r="A65" t="s">
         <v>136</v>
       </c>
@@ -3024,10 +3135,13 @@
         <v>10</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G65" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
       <c r="A66" t="s">
         <v>138</v>
       </c>
@@ -3044,10 +3158,13 @@
         <v>10</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G66" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
       <c r="A67" t="s">
         <v>140</v>
       </c>
@@ -3061,13 +3178,13 @@
         <v>9</v>
       </c>
       <c r="E67" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
       <c r="A68" t="s">
         <v>142</v>
       </c>
@@ -3084,10 +3201,13 @@
         <v>10</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G68" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
       <c r="A69" t="s">
         <v>144</v>
       </c>
@@ -3104,10 +3224,13 @@
         <v>10</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G69" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
       <c r="A70" t="s">
         <v>146</v>
       </c>
@@ -3124,10 +3247,13 @@
         <v>10</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G70" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
       <c r="A71" s="3" t="s">
         <v>148</v>
       </c>
@@ -3144,10 +3270,13 @@
         <v>10</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G71" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
       <c r="A72" s="3" t="s">
         <v>150</v>
       </c>
@@ -3164,10 +3293,13 @@
         <v>10</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G72" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
       <c r="A73" s="3" t="s">
         <v>152</v>
       </c>
@@ -3181,13 +3313,13 @@
         <v>9</v>
       </c>
       <c r="E73" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
       <c r="A74" s="3" t="s">
         <v>154</v>
       </c>
@@ -3204,10 +3336,13 @@
         <v>10</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G74" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
       <c r="A75" s="3" t="s">
         <v>156</v>
       </c>
@@ -3221,13 +3356,13 @@
         <v>9</v>
       </c>
       <c r="E75" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
       <c r="A76" t="s">
         <v>158</v>
       </c>
@@ -3244,10 +3379,13 @@
         <v>10</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G76" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
       <c r="A77" t="s">
         <v>160</v>
       </c>
@@ -3264,10 +3402,13 @@
         <v>10</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G77" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
       <c r="A78" t="s">
         <v>162</v>
       </c>
@@ -3284,10 +3425,13 @@
         <v>10</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G78" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
       <c r="A79" t="s">
         <v>164</v>
       </c>
@@ -3304,10 +3448,13 @@
         <v>10</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G79" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
       <c r="A80" t="s">
         <v>166</v>
       </c>
@@ -3324,10 +3471,13 @@
         <v>10</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G80" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
       <c r="A81" t="s">
         <v>168</v>
       </c>
@@ -3344,10 +3494,13 @@
         <v>10</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G81" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
       <c r="A82" t="s">
         <v>170</v>
       </c>
@@ -3361,13 +3514,13 @@
         <v>9</v>
       </c>
       <c r="E82" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
       <c r="A83" t="s">
         <v>172</v>
       </c>
@@ -3381,13 +3534,13 @@
         <v>9</v>
       </c>
       <c r="E83" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
       <c r="A84" t="s">
         <v>174</v>
       </c>
@@ -3404,10 +3557,13 @@
         <v>10</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G84" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
       <c r="A85" t="s">
         <v>176</v>
       </c>
@@ -3421,13 +3577,13 @@
         <v>9</v>
       </c>
       <c r="E85" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
       <c r="A86" t="s">
         <v>178</v>
       </c>
@@ -3441,13 +3597,13 @@
         <v>9</v>
       </c>
       <c r="E86" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
       <c r="A87" t="s">
         <v>166</v>
       </c>
@@ -3464,10 +3620,13 @@
         <v>10</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G87" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
       <c r="A88" t="s">
         <v>181</v>
       </c>
@@ -3484,10 +3643,13 @@
         <v>10</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G88" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
       <c r="A89" t="s">
         <v>183</v>
       </c>
@@ -3504,10 +3666,13 @@
         <v>10</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G89" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
       <c r="A90" t="s">
         <v>185</v>
       </c>
@@ -3524,10 +3689,13 @@
         <v>10</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G90" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
       <c r="A91" t="s">
         <v>187</v>
       </c>
@@ -3544,10 +3712,13 @@
         <v>10</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G91" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
       <c r="A92" t="s">
         <v>189</v>
       </c>
@@ -3564,10 +3735,13 @@
         <v>10</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G92" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
       <c r="A93" t="s">
         <v>191</v>
       </c>
@@ -3584,10 +3758,13 @@
         <v>10</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G93" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
       <c r="A94" t="s">
         <v>193</v>
       </c>
@@ -3604,10 +3781,13 @@
         <v>10</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G94" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
       <c r="A95" t="s">
         <v>195</v>
       </c>
@@ -3624,10 +3804,13 @@
         <v>10</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G95" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
       <c r="A96" t="s">
         <v>197</v>
       </c>
@@ -3644,10 +3827,13 @@
         <v>10</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G96" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
       <c r="A97" t="s">
         <v>199</v>
       </c>
@@ -3661,13 +3847,13 @@
         <v>9</v>
       </c>
       <c r="E97" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
       <c r="A98" t="s">
         <v>201</v>
       </c>
@@ -3681,13 +3867,13 @@
         <v>9</v>
       </c>
       <c r="E98" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
       <c r="A99" t="s">
         <v>203</v>
       </c>
@@ -3704,10 +3890,13 @@
         <v>10</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G99" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
       <c r="A100" t="s">
         <v>205</v>
       </c>
@@ -3721,13 +3910,13 @@
         <v>9</v>
       </c>
       <c r="E100" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
       <c r="A101" t="s">
         <v>207</v>
       </c>
@@ -3741,13 +3930,13 @@
         <v>9</v>
       </c>
       <c r="E101" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
       <c r="A102" t="s">
         <v>209</v>
       </c>
@@ -3761,13 +3950,13 @@
         <v>9</v>
       </c>
       <c r="E102" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
       <c r="A103" t="s">
         <v>211</v>
       </c>
@@ -3781,13 +3970,13 @@
         <v>9</v>
       </c>
       <c r="E103" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
       <c r="A104" t="s">
         <v>213</v>
       </c>
@@ -3801,13 +3990,13 @@
         <v>9</v>
       </c>
       <c r="E104" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
       <c r="A105" t="s">
         <v>215</v>
       </c>
@@ -3824,10 +4013,13 @@
         <v>10</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
+        <v>11</v>
+      </c>
+      <c r="G105" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
       <c r="A106" t="s">
         <v>217</v>
       </c>
@@ -3841,13 +4033,13 @@
         <v>9</v>
       </c>
       <c r="E106" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
       <c r="A107" t="s">
         <v>219</v>
       </c>
@@ -3861,13 +4053,13 @@
         <v>9</v>
       </c>
       <c r="E107" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
       <c r="A108" t="s">
         <v>221</v>
       </c>
@@ -3881,13 +4073,13 @@
         <v>9</v>
       </c>
       <c r="E108" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
       <c r="A109" t="s">
         <v>223</v>
       </c>
@@ -3901,13 +4093,13 @@
         <v>9</v>
       </c>
       <c r="E109" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
       <c r="A110" t="s">
         <v>225</v>
       </c>
@@ -3921,13 +4113,13 @@
         <v>9</v>
       </c>
       <c r="E110" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
       <c r="A111" t="s">
         <v>227</v>
       </c>
@@ -3941,13 +4133,13 @@
         <v>9</v>
       </c>
       <c r="E111" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
       <c r="A112" t="s">
         <v>229</v>
       </c>
@@ -3961,10 +4153,10 @@
         <v>9</v>
       </c>
       <c r="E112" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -3981,10 +4173,10 @@
         <v>9</v>
       </c>
       <c r="E113" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -4001,10 +4193,10 @@
         <v>9</v>
       </c>
       <c r="E114" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -4021,10 +4213,10 @@
         <v>9</v>
       </c>
       <c r="E115" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -4041,10 +4233,10 @@
         <v>9</v>
       </c>
       <c r="E116" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -4061,10 +4253,10 @@
         <v>9</v>
       </c>
       <c r="E117" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -4081,14 +4273,14 @@
         <v>9</v>
       </c>
       <c r="E118" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F117" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F118" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="A35">

--- a/testdata/listForExecution.xlsx
+++ b/testdata/listForExecution.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$122</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="258">
   <si>
     <t>TestName</t>
   </si>
@@ -759,6 +759,51 @@
   </si>
   <si>
     <t>C70881</t>
+  </si>
+  <si>
+    <t>Payments_Recipient-Edit_Recipient_[WEB]</t>
+  </si>
+  <si>
+    <t>C70882</t>
+  </si>
+  <si>
+    <t>Current_Accounts_RSD-Statements-Download_[WEB]</t>
+  </si>
+  <si>
+    <t>C70883</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Statements-Download_[WEB]</t>
+  </si>
+  <si>
+    <t>C70884</t>
+  </si>
+  <si>
+    <t>Savings_Accounts-Statements-Download_[WEB]</t>
+  </si>
+  <si>
+    <t>C70885</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-From_Current_Account_RSD_To_Current_Account_RSD_[WEB]</t>
+  </si>
+  <si>
+    <t>C70886</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-To_Card_[WEB]-From_Current_Domestic_Account</t>
+  </si>
+  <si>
+    <t>C70887</t>
+  </si>
+  <si>
+    <t>Payments-Own_Account_Transfer-To_Card_[WEB]-From_Savings_Account</t>
+  </si>
+  <si>
+    <t>C70888</t>
+  </si>
+  <si>
+    <t>4,</t>
   </si>
 </sst>
 </file>
@@ -1721,7 +1766,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="91.1388888888889" customWidth="1"/>
@@ -4279,8 +4324,148 @@
         <v>11</v>
       </c>
     </row>
+    <row r="119" spans="1:6">
+      <c r="A119" t="s">
+        <v>243</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E119" t="s">
+        <v>10</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
+      <c r="A120" t="s">
+        <v>245</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E120" t="s">
+        <v>10</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
+      <c r="A121" t="s">
+        <v>247</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E121" t="s">
+        <v>10</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
+      <c r="A122" t="s">
+        <v>249</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E122" t="s">
+        <v>10</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="A123" t="s">
+        <v>251</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E123" t="s">
+        <v>10</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
+      <c r="A124" t="s">
+        <v>253</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E124" t="s">
+        <v>10</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
+      <c r="A125" t="s">
+        <v>255</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E125" t="s">
+        <v>10</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F118" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F122" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="A35">

--- a/testdata/listForExecution.xlsx
+++ b/testdata/listForExecution.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$128</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="263">
   <si>
     <t>TestName</t>
   </si>
@@ -536,7 +536,7 @@
     <t>C70843</t>
   </si>
   <si>
-    <t>Credit_Cards-Transactions_Details[WEB]</t>
+    <t>Credit_Cards-Transactions_Details_[WEB]</t>
   </si>
   <si>
     <t>C70844</t>
@@ -803,7 +803,22 @@
     <t>C70888</t>
   </si>
   <si>
-    <t>4,</t>
+    <t>Current_Accounts_RSD-Statements-Empty_State_[WEB]</t>
+  </si>
+  <si>
+    <t>C70889</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts-Statements-Empty_State_[WEB]</t>
+  </si>
+  <si>
+    <t>C70890</t>
+  </si>
+  <si>
+    <t>Savings_Accounts-Statements-Empty_State_[WEB]</t>
+  </si>
+  <si>
+    <t>C70891</t>
   </si>
 </sst>
 </file>
@@ -1766,7 +1781,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G125"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="91.1388888888889" customWidth="1"/>
@@ -4452,20 +4467,80 @@
         <v>256</v>
       </c>
       <c r="C125" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E125" t="s">
+        <v>10</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="A126" t="s">
         <v>257</v>
       </c>
-      <c r="D125" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E125" t="s">
-        <v>10</v>
-      </c>
-      <c r="F125" s="1" t="s">
+      <c r="B126" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E126" t="s">
+        <v>10</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="A127" t="s">
+        <v>259</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E127" t="s">
+        <v>10</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="A128" t="s">
+        <v>261</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E128" t="s">
+        <v>10</v>
+      </c>
+      <c r="F128" s="1" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F122" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F128" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="A35">

--- a/testdata/listForExecution.xlsx
+++ b/testdata/listForExecution.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$129</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="273">
   <si>
     <t>TestName</t>
   </si>
@@ -819,6 +819,36 @@
   </si>
   <si>
     <t>C70891</t>
+  </si>
+  <si>
+    <t>Savings_Accounts-Transactions_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70892</t>
+  </si>
+  <si>
+    <t>Cards-Transactions_Details_[WEB]-Debit_Cards</t>
+  </si>
+  <si>
+    <t>C70893</t>
+  </si>
+  <si>
+    <t>Cards-Transactions_Details_[WEB]-Credit_Cards</t>
+  </si>
+  <si>
+    <t>C70894</t>
+  </si>
+  <si>
+    <t>Savings_accounts-Transactions_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70895</t>
+  </si>
+  <si>
+    <t>Payments-Upcoming_Payments-List_Of_Transactions_[WEB]</t>
+  </si>
+  <si>
+    <t>C70896</t>
   </si>
 </sst>
 </file>
@@ -1781,7 +1811,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G128"/>
+  <dimension ref="A1:G133"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="91.1388888888889" customWidth="1"/>
@@ -4539,8 +4569,108 @@
         <v>11</v>
       </c>
     </row>
+    <row r="129" spans="1:6">
+      <c r="A129" t="s">
+        <v>263</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E129" t="s">
+        <v>10</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="A130" t="s">
+        <v>265</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E130" t="s">
+        <v>10</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
+      <c r="A131" t="s">
+        <v>267</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E131" t="s">
+        <v>10</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="A132" t="s">
+        <v>269</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E132" t="s">
+        <v>10</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="A133" t="s">
+        <v>271</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E133" t="s">
+        <v>10</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F128" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F129" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="A35">

--- a/testdata/listForExecution.xlsx
+++ b/testdata/listForExecution.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="20490" windowHeight="7500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$133</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1493,7 +1493,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1812,12 +1812,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G133"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="91.1388888888889" customWidth="1"/>
+    <col min="1" max="1" width="91.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1854,13 +1854,13 @@
         <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1949,7 +1949,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -1969,7 +1969,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -2058,7 +2058,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -2078,7 +2078,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -2098,7 +2098,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -2118,7 +2118,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -2158,7 +2158,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -2270,7 +2270,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:6">
       <c r="A22" s="3" t="s">
         <v>50</v>
       </c>
@@ -2290,7 +2290,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>52</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:6">
       <c r="A40" t="s">
         <v>86</v>
       </c>
@@ -2698,7 +2698,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
         <v>88</v>
       </c>
@@ -2787,7 +2787,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:6">
       <c r="A45" t="s">
         <v>96</v>
       </c>
@@ -2807,7 +2807,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:6">
       <c r="A46" t="s">
         <v>98</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:6">
       <c r="A48" t="s">
         <v>102</v>
       </c>
@@ -2870,7 +2870,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
         <v>104</v>
       </c>
@@ -2913,7 +2913,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:6">
       <c r="A51" t="s">
         <v>108</v>
       </c>
@@ -2933,7 +2933,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:6">
       <c r="A52" t="s">
         <v>110</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
         <v>112</v>
       </c>
@@ -2973,7 +2973,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
         <v>114</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:6">
       <c r="A58" t="s">
         <v>122</v>
       </c>
@@ -3082,7 +3082,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:6">
       <c r="A59" t="s">
         <v>124</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:6">
       <c r="A60" t="s">
         <v>126</v>
       </c>
@@ -3122,7 +3122,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:6">
       <c r="A61" t="s">
         <v>128</v>
       </c>
@@ -3142,7 +3142,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:6">
       <c r="A62" t="s">
         <v>130</v>
       </c>
@@ -3254,7 +3254,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:6">
       <c r="A67" t="s">
         <v>140</v>
       </c>
@@ -3389,7 +3389,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:6">
       <c r="A73" s="3" t="s">
         <v>152</v>
       </c>
@@ -3432,7 +3432,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:6">
       <c r="A75" s="3" t="s">
         <v>156</v>
       </c>
@@ -3590,7 +3590,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:6">
       <c r="A82" t="s">
         <v>170</v>
       </c>
@@ -3610,7 +3610,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:6">
       <c r="A83" t="s">
         <v>172</v>
       </c>
@@ -3653,7 +3653,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:6">
       <c r="A85" t="s">
         <v>176</v>
       </c>
@@ -3673,7 +3673,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:6">
       <c r="A86" t="s">
         <v>178</v>
       </c>
@@ -3923,7 +3923,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:6">
       <c r="A97" t="s">
         <v>199</v>
       </c>
@@ -3943,7 +3943,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" spans="1:6">
       <c r="A98" t="s">
         <v>201</v>
       </c>
@@ -3986,7 +3986,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" spans="1:6">
       <c r="A100" t="s">
         <v>205</v>
       </c>
@@ -4006,7 +4006,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" spans="1:6">
       <c r="A101" t="s">
         <v>207</v>
       </c>
@@ -4026,7 +4026,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:6">
       <c r="A102" t="s">
         <v>209</v>
       </c>
@@ -4046,7 +4046,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:6">
       <c r="A103" t="s">
         <v>211</v>
       </c>
@@ -4066,7 +4066,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" spans="1:6">
       <c r="A104" t="s">
         <v>213</v>
       </c>
@@ -4109,7 +4109,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" spans="1:6">
       <c r="A106" t="s">
         <v>217</v>
       </c>
@@ -4129,7 +4129,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" spans="1:6">
       <c r="A107" t="s">
         <v>219</v>
       </c>
@@ -4149,7 +4149,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" spans="1:6">
       <c r="A108" t="s">
         <v>221</v>
       </c>
@@ -4169,7 +4169,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" spans="1:6">
       <c r="A109" t="s">
         <v>223</v>
       </c>
@@ -4189,7 +4189,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:6">
       <c r="A110" t="s">
         <v>225</v>
       </c>
@@ -4209,7 +4209,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:6">
       <c r="A111" t="s">
         <v>227</v>
       </c>
@@ -4229,7 +4229,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" spans="1:6">
       <c r="A112" t="s">
         <v>229</v>
       </c>
@@ -4670,7 +4670,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F129" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F133" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="A35">

--- a/testdata/listForExecution.xlsx
+++ b/testdata/listForExecution.xlsx
@@ -4,14 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$133</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -30,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="282">
   <si>
     <t>TestName</t>
   </si>
@@ -849,6 +846,33 @@
   </si>
   <si>
     <t>C70896</t>
+  </si>
+  <si>
+    <t>Payments-Upcoming_Payments-Cancel_Payments_[WEB]</t>
+  </si>
+  <si>
+    <t>C70897</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Details-Financial_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70898</t>
+  </si>
+  <si>
+    <t>Loan_Accounts-Details-Account_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3, </t>
+  </si>
+  <si>
+    <t>Payments_Payments_Archive-Payments_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70900</t>
   </si>
 </sst>
 </file>
@@ -861,7 +885,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -874,11 +898,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <charset val="238"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -1343,143 +1362,142 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1493,7 +1511,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1811,10 +1829,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G133"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="6"/>
+  <dimension ref="A1:F137"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="91.1428571428571" customWidth="1"/>
+    <col min="1" max="1" width="91.1388888888889" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1837,8 +1855,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:7">
-      <c r="A2" s="1" t="s">
+    <row r="2" s="1" customFormat="1" spans="1:6">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1854,9 +1872,6 @@
         <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1880,7 +1895,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1899,11 +1914,8 @@
       <c r="F4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1922,11 +1934,8 @@
       <c r="F5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -1943,9 +1952,6 @@
         <v>10</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1989,7 +1995,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -2008,11 +2014,8 @@
       <c r="F9" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -2031,11 +2034,8 @@
       <c r="F10" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -2052,9 +2052,6 @@
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" s="1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2178,7 +2175,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -2197,11 +2194,8 @@
       <c r="F18" t="s">
         <v>11</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -2220,11 +2214,8 @@
       <c r="F19" t="s">
         <v>11</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -2243,11 +2234,8 @@
       <c r="F20" t="s">
         <v>11</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -2266,12 +2254,9 @@
       <c r="F21" t="s">
         <v>11</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="3" t="s">
+      <c r="A22" t="s">
         <v>50</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -2310,7 +2295,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -2329,11 +2314,8 @@
       <c r="F24" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G24" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -2352,11 +2334,8 @@
       <c r="F25" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G25" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -2375,12 +2354,9 @@
       <c r="F26" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G26" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="3" t="s">
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
         <v>60</v>
       </c>
       <c r="B27" s="2" t="s">
@@ -2398,11 +2374,8 @@
       <c r="F27" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G27" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>62</v>
       </c>
@@ -2421,11 +2394,8 @@
       <c r="F28" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G28" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>64</v>
       </c>
@@ -2444,11 +2414,8 @@
       <c r="F29" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G29" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -2467,11 +2434,8 @@
       <c r="F30" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G30" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
         <v>68</v>
       </c>
@@ -2490,11 +2454,8 @@
       <c r="F31" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G31" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
         <v>70</v>
       </c>
@@ -2513,11 +2474,8 @@
       <c r="F32" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G32" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
         <v>72</v>
       </c>
@@ -2536,11 +2494,8 @@
       <c r="F33" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G33" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
         <v>74</v>
       </c>
@@ -2559,11 +2514,8 @@
       <c r="F34" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G34" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
         <v>76</v>
       </c>
@@ -2582,11 +2534,8 @@
       <c r="F35" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G35" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
         <v>78</v>
       </c>
@@ -2605,11 +2554,8 @@
       <c r="F36" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G36" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
         <v>80</v>
       </c>
@@ -2628,11 +2574,8 @@
       <c r="F37" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G37" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
         <v>82</v>
       </c>
@@ -2651,11 +2594,8 @@
       <c r="F38" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G38" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
         <v>84</v>
       </c>
@@ -2672,9 +2612,6 @@
         <v>10</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G39" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2718,7 +2655,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
         <v>90</v>
       </c>
@@ -2737,11 +2674,8 @@
       <c r="F42" t="s">
         <v>11</v>
       </c>
-      <c r="G42" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43" t="s">
         <v>92</v>
       </c>
@@ -2760,11 +2694,8 @@
       <c r="F43" t="s">
         <v>11</v>
       </c>
-      <c r="G43" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44" t="s">
         <v>94</v>
       </c>
@@ -2781,9 +2712,6 @@
         <v>10</v>
       </c>
       <c r="F44" t="s">
-        <v>11</v>
-      </c>
-      <c r="G44" s="1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2827,7 +2755,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
         <v>100</v>
       </c>
@@ -2844,9 +2772,6 @@
         <v>10</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G47" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2867,7 +2792,7 @@
         <v>10</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -2890,7 +2815,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:6">
       <c r="A50" t="s">
         <v>106</v>
       </c>
@@ -2907,9 +2832,6 @@
         <v>10</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G50" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2993,7 +2915,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:6">
       <c r="A55" t="s">
         <v>116</v>
       </c>
@@ -3012,11 +2934,8 @@
       <c r="F55" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G55" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
+    </row>
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
         <v>118</v>
       </c>
@@ -3035,11 +2954,8 @@
       <c r="F56" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G56" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
+    </row>
+    <row r="57" spans="1:6">
       <c r="A57" t="s">
         <v>120</v>
       </c>
@@ -3056,9 +2972,6 @@
         <v>10</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G57" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3162,7 +3075,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:6">
       <c r="A63" t="s">
         <v>132</v>
       </c>
@@ -3181,11 +3094,8 @@
       <c r="F63" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G63" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7">
+    </row>
+    <row r="64" spans="1:6">
       <c r="A64" t="s">
         <v>134</v>
       </c>
@@ -3204,11 +3114,8 @@
       <c r="F64" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G64" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
+    </row>
+    <row r="65" spans="1:6">
       <c r="A65" t="s">
         <v>136</v>
       </c>
@@ -3227,11 +3134,8 @@
       <c r="F65" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G65" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
+    </row>
+    <row r="66" spans="1:6">
       <c r="A66" t="s">
         <v>138</v>
       </c>
@@ -3248,9 +3152,6 @@
         <v>10</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G66" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3274,7 +3175,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:6">
       <c r="A68" t="s">
         <v>142</v>
       </c>
@@ -3293,11 +3194,8 @@
       <c r="F68" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G68" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7">
+    </row>
+    <row r="69" spans="1:6">
       <c r="A69" t="s">
         <v>144</v>
       </c>
@@ -3316,11 +3214,8 @@
       <c r="F69" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G69" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7">
+    </row>
+    <row r="70" spans="1:6">
       <c r="A70" t="s">
         <v>146</v>
       </c>
@@ -3339,12 +3234,9 @@
       <c r="F70" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G70" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7">
-      <c r="A71" s="3" t="s">
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" t="s">
         <v>148</v>
       </c>
       <c r="B71" s="2" t="s">
@@ -3362,12 +3254,9 @@
       <c r="F71" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G71" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7">
-      <c r="A72" s="3" t="s">
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" t="s">
         <v>150</v>
       </c>
       <c r="B72" s="2" t="s">
@@ -3385,12 +3274,9 @@
       <c r="F72" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G72" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="73" spans="1:6">
-      <c r="A73" s="3" t="s">
+      <c r="A73" t="s">
         <v>152</v>
       </c>
       <c r="B73" s="2" t="s">
@@ -3409,8 +3295,8 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="1:7">
-      <c r="A74" s="3" t="s">
+    <row r="74" spans="1:6">
+      <c r="A74" t="s">
         <v>154</v>
       </c>
       <c r="B74" s="2" t="s">
@@ -3428,12 +3314,9 @@
       <c r="F74" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G74" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="75" spans="1:6">
-      <c r="A75" s="3" t="s">
+      <c r="A75" t="s">
         <v>156</v>
       </c>
       <c r="B75" s="2" t="s">
@@ -3452,7 +3335,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:6">
       <c r="A76" t="s">
         <v>158</v>
       </c>
@@ -3471,11 +3354,8 @@
       <c r="F76" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G76" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7">
+    </row>
+    <row r="77" spans="1:6">
       <c r="A77" t="s">
         <v>160</v>
       </c>
@@ -3494,11 +3374,8 @@
       <c r="F77" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G77" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7">
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78" t="s">
         <v>162</v>
       </c>
@@ -3517,11 +3394,8 @@
       <c r="F78" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G78" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7">
+    </row>
+    <row r="79" spans="1:6">
       <c r="A79" t="s">
         <v>164</v>
       </c>
@@ -3540,11 +3414,8 @@
       <c r="F79" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G79" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7">
+    </row>
+    <row r="80" spans="1:6">
       <c r="A80" t="s">
         <v>166</v>
       </c>
@@ -3563,11 +3434,8 @@
       <c r="F80" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G80" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7">
+    </row>
+    <row r="81" spans="1:6">
       <c r="A81" t="s">
         <v>168</v>
       </c>
@@ -3584,9 +3452,6 @@
         <v>10</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G81" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3630,7 +3495,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:6">
       <c r="A84" t="s">
         <v>174</v>
       </c>
@@ -3647,9 +3512,6 @@
         <v>10</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G84" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3693,7 +3555,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:6">
       <c r="A87" t="s">
         <v>166</v>
       </c>
@@ -3712,11 +3574,8 @@
       <c r="F87" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G87" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7">
+    </row>
+    <row r="88" spans="1:6">
       <c r="A88" t="s">
         <v>181</v>
       </c>
@@ -3735,11 +3594,8 @@
       <c r="F88" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G88" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7">
+    </row>
+    <row r="89" spans="1:6">
       <c r="A89" t="s">
         <v>183</v>
       </c>
@@ -3758,11 +3614,8 @@
       <c r="F89" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G89" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7">
+    </row>
+    <row r="90" spans="1:6">
       <c r="A90" t="s">
         <v>185</v>
       </c>
@@ -3781,11 +3634,8 @@
       <c r="F90" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G90" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7">
+    </row>
+    <row r="91" spans="1:6">
       <c r="A91" t="s">
         <v>187</v>
       </c>
@@ -3804,11 +3654,8 @@
       <c r="F91" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G91" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7">
+    </row>
+    <row r="92" spans="1:6">
       <c r="A92" t="s">
         <v>189</v>
       </c>
@@ -3827,11 +3674,8 @@
       <c r="F92" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G92" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7">
+    </row>
+    <row r="93" spans="1:6">
       <c r="A93" t="s">
         <v>191</v>
       </c>
@@ -3850,11 +3694,8 @@
       <c r="F93" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G93" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7">
+    </row>
+    <row r="94" spans="1:6">
       <c r="A94" t="s">
         <v>193</v>
       </c>
@@ -3873,11 +3714,8 @@
       <c r="F94" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G94" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7">
+    </row>
+    <row r="95" spans="1:6">
       <c r="A95" t="s">
         <v>195</v>
       </c>
@@ -3896,11 +3734,8 @@
       <c r="F95" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G95" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7">
+    </row>
+    <row r="96" spans="1:6">
       <c r="A96" t="s">
         <v>197</v>
       </c>
@@ -3917,9 +3752,6 @@
         <v>10</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G96" t="s">
         <v>11</v>
       </c>
     </row>
@@ -3963,7 +3795,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" spans="1:6">
       <c r="A99" t="s">
         <v>203</v>
       </c>
@@ -3980,9 +3812,6 @@
         <v>10</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G99" t="s">
         <v>11</v>
       </c>
     </row>
@@ -4086,7 +3915,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" spans="1:6">
       <c r="A105" t="s">
         <v>215</v>
       </c>
@@ -4103,9 +3932,6 @@
         <v>10</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G105" t="s">
         <v>11</v>
       </c>
     </row>
@@ -4669,43 +4495,89 @@
         <v>11</v>
       </c>
     </row>
+    <row r="134" customFormat="1" spans="1:6">
+      <c r="A134" t="s">
+        <v>273</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E134" t="s">
+        <v>10</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="135" customFormat="1" spans="1:6">
+      <c r="A135" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E135" t="s">
+        <v>10</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="136" customFormat="1" spans="1:6">
+      <c r="A136" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E136" t="s">
+        <v>10</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="137" customFormat="1" spans="1:6">
+      <c r="A137" t="s">
+        <v>280</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E137" t="s">
+        <v>10</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F133" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
-  <conditionalFormatting sqref="A35">
-    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A69">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A74">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A75">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A80">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A70:A71">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A78:A79">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B$1:B$1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A68 A81:A1048576 A76:A77 A72:A73">
-    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/testdata/listForExecution.xlsx
+++ b/testdata/listForExecution.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="28800" windowHeight="11580"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="284">
   <si>
     <t>TestName</t>
   </si>
@@ -873,6 +873,12 @@
   </si>
   <si>
     <t>C70900</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_Internal_Urgent_Payment_[WEB]</t>
+  </si>
+  <si>
+    <t>C70901</t>
   </si>
 </sst>
 </file>
@@ -1829,10 +1835,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F137"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <dimension ref="A1:F138"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="91.1388888888889" customWidth="1"/>
+    <col min="1" max="1" width="91.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -4572,6 +4578,26 @@
         <v>10</v>
       </c>
       <c r="F137" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="A138" t="s">
+        <v>282</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C138" s="1">
+        <v>3</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E138" t="s">
+        <v>10</v>
+      </c>
+      <c r="F138" s="1" t="s">
         <v>11</v>
       </c>
     </row>

--- a/testdata/listForExecution.xlsx
+++ b/testdata/listForExecution.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="286">
   <si>
     <t>TestName</t>
   </si>
@@ -879,6 +879,12 @@
   </si>
   <si>
     <t>C70901</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_Internal_Non_Urgent_Payment_[WEB]</t>
+  </si>
+  <si>
+    <t>C70902</t>
   </si>
 </sst>
 </file>
@@ -1835,7 +1841,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F138"/>
+  <dimension ref="A1:F139"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="91.1428571428571" customWidth="1"/>
@@ -4601,6 +4607,26 @@
         <v>11</v>
       </c>
     </row>
+    <row r="139" spans="1:6">
+      <c r="A139" t="s">
+        <v>284</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C139" s="1">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E139" t="s">
+        <v>10</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B$1:B$1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/testdata/listForExecution.xlsx
+++ b/testdata/listForExecution.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="304">
   <si>
     <t>TestName</t>
   </si>
@@ -885,6 +885,60 @@
   </si>
   <si>
     <t>C70902</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Urgent_Payment_No_Model_[WEB]</t>
+  </si>
+  <si>
+    <t>C70903</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Urgent_Payment_Model11_Invalid_Bez_Poziva_Na_Broj_[WEB]</t>
+  </si>
+  <si>
+    <t>C70904</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Non_Urgent_Payment_Model11_[WEB]</t>
+  </si>
+  <si>
+    <t>C70905</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Urgent_Payment_Model97_Invalid_Bez_Poziva_Na_Broj_[WEB]</t>
+  </si>
+  <si>
+    <t>C70906</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Non_Urgent_Payment_Model97_[WEB]</t>
+  </si>
+  <si>
+    <t>C70907</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_Budzetski_Urgent_Payment_Purpose_Code_289_Invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70908</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_Budzetski_Urgent_Payment_Without_Reference_Number_Invalid_[WEB]</t>
+  </si>
+  <si>
+    <t>C70909</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_Budzetski_Urgent_Payment_Model97_[WEB]</t>
+  </si>
+  <si>
+    <t>C70910</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_Budzetski_Non_Urgent_Payment_Model97_[WEB]</t>
+  </si>
+  <si>
+    <t>C70911</t>
   </si>
 </sst>
 </file>
@@ -1841,10 +1895,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F139"/>
+  <dimension ref="A1:F148"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="91.1428571428571" customWidth="1"/>
+    <col min="1" max="1" width="94.1428571428571" customWidth="1"/>
+    <col min="2" max="2" width="11.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -4624,6 +4679,186 @@
         <v>10</v>
       </c>
       <c r="F139" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="A140" t="s">
+        <v>286</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C140" s="1">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E140" t="s">
+        <v>10</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="A141" t="s">
+        <v>288</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C141" s="1">
+        <v>3</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E141" t="s">
+        <v>10</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="A142" t="s">
+        <v>290</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C142" s="1">
+        <v>3</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E142" t="s">
+        <v>10</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="A143" t="s">
+        <v>292</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C143" s="1">
+        <v>3</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E143" t="s">
+        <v>10</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
+      <c r="A144" t="s">
+        <v>294</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C144" s="1">
+        <v>3</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E144" t="s">
+        <v>10</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="A145" t="s">
+        <v>296</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C145" s="1">
+        <v>3</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E145" t="s">
+        <v>10</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
+      <c r="A146" t="s">
+        <v>298</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C146" s="1">
+        <v>3</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E146" t="s">
+        <v>10</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
+      <c r="A147" t="s">
+        <v>300</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C147" s="1">
+        <v>3</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E147" t="s">
+        <v>10</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="A148" t="s">
+        <v>302</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C148" s="1">
+        <v>3</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E148" t="s">
+        <v>10</v>
+      </c>
+      <c r="F148" s="1" t="s">
         <v>11</v>
       </c>
     </row>

--- a/testdata/listForExecution.xlsx
+++ b/testdata/listForExecution.xlsx
@@ -4,11 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11580"/>
+    <workbookView windowWidth="13128" windowHeight="8232"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$148</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="309">
   <si>
     <t>TestName</t>
   </si>
@@ -875,70 +878,85 @@
     <t>C70900</t>
   </si>
   <si>
-    <t>Payments_Domestic_Payments_Internal_Urgent_Payment_[WEB]</t>
+    <t>Payments_Currency_Exchange_Pricelist_[WEB]-Overview</t>
   </si>
   <si>
     <t>C70901</t>
   </si>
   <si>
-    <t>Payments_Domestic_Payments_Internal_Non_Urgent_Payment_[WEB]</t>
+    <t>Saving_Accounts_Transactions_Download_Option_[WEB]</t>
   </si>
   <si>
     <t>C70902</t>
   </si>
   <si>
-    <t>Payments_Domestic_Payments_External_Urgent_Payment_No_Model_[WEB]</t>
+    <t>Payments_Own_Account_Transfer_To_Loan_[WEB]</t>
   </si>
   <si>
     <t>C70903</t>
   </si>
   <si>
-    <t>Payments_Domestic_Payments_External_Urgent_Payment_Model11_Invalid_Bez_Poziva_Na_Broj_[WEB]</t>
+    <t>Payments_Own_Account_Transfer_From_Current_Foreign_Account_To_Current_Foreign_Account_[WEB]</t>
   </si>
   <si>
     <t>C70904</t>
   </si>
   <si>
-    <t>Payments_Domestic_Payments_External_Non_Urgent_Payment_Model11_[WEB]</t>
+    <t>Payments_Currency_Exchange_[WEB]-Buy_From_Payment</t>
   </si>
   <si>
     <t>C70905</t>
   </si>
   <si>
-    <t>Payments_Domestic_Payments_External_Urgent_Payment_Model97_Invalid_Bez_Poziva_Na_Broj_[WEB]</t>
+    <t>Payments_Currency_Exchange_[WEB]-Sell_From_Payment</t>
   </si>
   <si>
     <t>C70906</t>
   </si>
   <si>
-    <t>Payments_Domestic_Payments_External_Non_Urgent_Payment_Model97_[WEB]</t>
+    <t>Savings_Accounts_Transactions_Filter_By_Date_Date_Picker_[WEB]</t>
   </si>
   <si>
     <t>C70907</t>
   </si>
   <si>
-    <t>Payments_Domestic_Payments_Budzetski_Urgent_Payment_Purpose_Code_289_Invalid_[WEB]</t>
+    <t>Payments_Recipient_Template_List_[WEB]</t>
   </si>
   <si>
     <t>C70908</t>
   </si>
   <si>
-    <t>Payments_Domestic_Payments_Budzetski_Urgent_Payment_Without_Reference_Number_Invalid_[WEB]</t>
+    <t>Payments_Upcoming_Payments_Details_Of_Payments_Transaction_On_The_List_Of_Transaction_[WEB]</t>
   </si>
   <si>
     <t>C70909</t>
   </si>
   <si>
-    <t>Payments_Domestic_Payments_Budzetski_Urgent_Payment_Model97_[WEB]</t>
-  </si>
-  <si>
     <t>C70910</t>
   </si>
   <si>
-    <t>Payments_Domestic_Payments_Budzetski_Non_Urgent_Payment_Model97_[WEB]</t>
+    <t>Payments_Payments_Archive_Payments_Details_[WEB]</t>
   </si>
   <si>
     <t>C70911</t>
+  </si>
+  <si>
+    <t>Current_Accounts_RSD_Statemants_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70912</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts_Statemants_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70913</t>
+  </si>
+  <si>
+    <t>Saving_Accounts_Accounts_Statemants_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70914</t>
   </si>
 </sst>
 </file>
@@ -1895,14 +1913,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F148"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
+  <dimension ref="A1:F151"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="94.1428571428571" customWidth="1"/>
-    <col min="2" max="2" width="11.7142857142857" customWidth="1"/>
+    <col min="1" max="1" width="91.1388888888889" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" customFormat="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1942,7 +1959,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" customFormat="1" spans="1:6">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1962,7 +1979,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" customFormat="1" spans="1:6">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1982,7 +1999,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" customFormat="1" spans="1:6">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -2002,7 +2019,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" customFormat="1" spans="1:6">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -2022,7 +2039,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" customFormat="1" spans="1:6">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -2042,7 +2059,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" customFormat="1" spans="1:6">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -2062,7 +2079,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" customFormat="1" spans="1:6">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -2082,7 +2099,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" customFormat="1" spans="1:6">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -2102,7 +2119,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" customFormat="1" spans="1:6">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -2122,7 +2139,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" customFormat="1" spans="1:6">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -2142,7 +2159,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" customFormat="1" spans="1:6">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -2162,7 +2179,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" customFormat="1" spans="1:6">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -2182,7 +2199,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" customFormat="1" spans="1:6">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -2202,7 +2219,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" customFormat="1" spans="1:6">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -2222,7 +2239,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" customFormat="1" spans="1:6">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -2242,7 +2259,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" customFormat="1" spans="1:6">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -2262,7 +2279,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" customFormat="1" spans="1:6">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -2282,7 +2299,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" customFormat="1" spans="1:6">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -2302,7 +2319,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" customFormat="1" spans="1:6">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -2322,7 +2339,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" customFormat="1" spans="1:6">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -2342,7 +2359,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" customFormat="1" spans="1:6">
       <c r="A23" t="s">
         <v>52</v>
       </c>
@@ -2362,7 +2379,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" customFormat="1" spans="1:6">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -2382,7 +2399,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" customFormat="1" spans="1:6">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -2402,7 +2419,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" customFormat="1" spans="1:6">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -2422,7 +2439,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" customFormat="1" spans="1:6">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -2442,7 +2459,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" customFormat="1" spans="1:6">
       <c r="A28" t="s">
         <v>62</v>
       </c>
@@ -2462,7 +2479,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" customFormat="1" spans="1:6">
       <c r="A29" t="s">
         <v>64</v>
       </c>
@@ -2482,7 +2499,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" customFormat="1" spans="1:6">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -2502,7 +2519,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" customFormat="1" spans="1:6">
       <c r="A31" t="s">
         <v>68</v>
       </c>
@@ -2522,7 +2539,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" customFormat="1" spans="1:6">
       <c r="A32" t="s">
         <v>70</v>
       </c>
@@ -2542,7 +2559,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" customFormat="1" spans="1:6">
       <c r="A33" t="s">
         <v>72</v>
       </c>
@@ -2562,7 +2579,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" customFormat="1" spans="1:6">
       <c r="A34" t="s">
         <v>74</v>
       </c>
@@ -2582,7 +2599,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" customFormat="1" spans="1:6">
       <c r="A35" t="s">
         <v>76</v>
       </c>
@@ -2602,7 +2619,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" customFormat="1" spans="1:6">
       <c r="A36" t="s">
         <v>78</v>
       </c>
@@ -2622,7 +2639,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" customFormat="1" spans="1:6">
       <c r="A37" t="s">
         <v>80</v>
       </c>
@@ -2642,7 +2659,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" customFormat="1" spans="1:6">
       <c r="A38" t="s">
         <v>82</v>
       </c>
@@ -2662,7 +2679,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" customFormat="1" spans="1:6">
       <c r="A39" t="s">
         <v>84</v>
       </c>
@@ -2682,7 +2699,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" customFormat="1" spans="1:6">
       <c r="A40" t="s">
         <v>86</v>
       </c>
@@ -2702,7 +2719,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" customFormat="1" spans="1:6">
       <c r="A41" t="s">
         <v>88</v>
       </c>
@@ -2722,7 +2739,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" customFormat="1" spans="1:6">
       <c r="A42" t="s">
         <v>90</v>
       </c>
@@ -2742,7 +2759,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" customFormat="1" spans="1:6">
       <c r="A43" t="s">
         <v>92</v>
       </c>
@@ -2762,7 +2779,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" customFormat="1" spans="1:6">
       <c r="A44" t="s">
         <v>94</v>
       </c>
@@ -2782,7 +2799,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" customFormat="1" spans="1:6">
       <c r="A45" t="s">
         <v>96</v>
       </c>
@@ -2802,7 +2819,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" customFormat="1" spans="1:6">
       <c r="A46" t="s">
         <v>98</v>
       </c>
@@ -2822,7 +2839,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" customFormat="1" spans="1:6">
       <c r="A47" t="s">
         <v>100</v>
       </c>
@@ -2842,7 +2859,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" customFormat="1" spans="1:6">
       <c r="A48" t="s">
         <v>102</v>
       </c>
@@ -2862,7 +2879,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" customFormat="1" spans="1:6">
       <c r="A49" t="s">
         <v>104</v>
       </c>
@@ -2882,7 +2899,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" customFormat="1" spans="1:6">
       <c r="A50" t="s">
         <v>106</v>
       </c>
@@ -2902,7 +2919,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" customFormat="1" spans="1:6">
       <c r="A51" t="s">
         <v>108</v>
       </c>
@@ -2922,7 +2939,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" customFormat="1" spans="1:6">
       <c r="A52" t="s">
         <v>110</v>
       </c>
@@ -2942,7 +2959,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" customFormat="1" spans="1:6">
       <c r="A53" t="s">
         <v>112</v>
       </c>
@@ -2962,7 +2979,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" customFormat="1" spans="1:6">
       <c r="A54" t="s">
         <v>114</v>
       </c>
@@ -2982,7 +2999,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" customFormat="1" spans="1:6">
       <c r="A55" t="s">
         <v>116</v>
       </c>
@@ -3002,7 +3019,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" customFormat="1" spans="1:6">
       <c r="A56" t="s">
         <v>118</v>
       </c>
@@ -3022,7 +3039,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" customFormat="1" spans="1:6">
       <c r="A57" t="s">
         <v>120</v>
       </c>
@@ -3042,7 +3059,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" customFormat="1" spans="1:6">
       <c r="A58" t="s">
         <v>122</v>
       </c>
@@ -3062,7 +3079,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" customFormat="1" spans="1:6">
       <c r="A59" t="s">
         <v>124</v>
       </c>
@@ -3082,7 +3099,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" customFormat="1" spans="1:6">
       <c r="A60" t="s">
         <v>126</v>
       </c>
@@ -3102,7 +3119,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" customFormat="1" spans="1:6">
       <c r="A61" t="s">
         <v>128</v>
       </c>
@@ -3122,7 +3139,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" customFormat="1" spans="1:6">
       <c r="A62" t="s">
         <v>130</v>
       </c>
@@ -3142,7 +3159,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" customFormat="1" spans="1:6">
       <c r="A63" t="s">
         <v>132</v>
       </c>
@@ -3162,7 +3179,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" customFormat="1" spans="1:6">
       <c r="A64" t="s">
         <v>134</v>
       </c>
@@ -3182,7 +3199,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" customFormat="1" spans="1:6">
       <c r="A65" t="s">
         <v>136</v>
       </c>
@@ -3202,7 +3219,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" customFormat="1" spans="1:6">
       <c r="A66" t="s">
         <v>138</v>
       </c>
@@ -3222,7 +3239,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" customFormat="1" spans="1:6">
       <c r="A67" t="s">
         <v>140</v>
       </c>
@@ -3242,7 +3259,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" customFormat="1" spans="1:6">
       <c r="A68" t="s">
         <v>142</v>
       </c>
@@ -3262,7 +3279,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" customFormat="1" spans="1:6">
       <c r="A69" t="s">
         <v>144</v>
       </c>
@@ -3282,7 +3299,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" customFormat="1" spans="1:6">
       <c r="A70" t="s">
         <v>146</v>
       </c>
@@ -3302,7 +3319,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" customFormat="1" spans="1:6">
       <c r="A71" t="s">
         <v>148</v>
       </c>
@@ -3322,7 +3339,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" customFormat="1" spans="1:6">
       <c r="A72" t="s">
         <v>150</v>
       </c>
@@ -3342,7 +3359,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" customFormat="1" spans="1:6">
       <c r="A73" t="s">
         <v>152</v>
       </c>
@@ -3362,7 +3379,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" customFormat="1" spans="1:6">
       <c r="A74" t="s">
         <v>154</v>
       </c>
@@ -3382,7 +3399,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" customFormat="1" spans="1:6">
       <c r="A75" t="s">
         <v>156</v>
       </c>
@@ -3402,7 +3419,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" customFormat="1" spans="1:6">
       <c r="A76" t="s">
         <v>158</v>
       </c>
@@ -3422,7 +3439,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" customFormat="1" spans="1:6">
       <c r="A77" t="s">
         <v>160</v>
       </c>
@@ -3442,7 +3459,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" customFormat="1" spans="1:6">
       <c r="A78" t="s">
         <v>162</v>
       </c>
@@ -3462,7 +3479,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" customFormat="1" spans="1:6">
       <c r="A79" t="s">
         <v>164</v>
       </c>
@@ -3482,7 +3499,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" customFormat="1" spans="1:6">
       <c r="A80" t="s">
         <v>166</v>
       </c>
@@ -3502,7 +3519,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" customFormat="1" spans="1:6">
       <c r="A81" t="s">
         <v>168</v>
       </c>
@@ -3522,7 +3539,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" customFormat="1" spans="1:6">
       <c r="A82" t="s">
         <v>170</v>
       </c>
@@ -3542,7 +3559,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" customFormat="1" spans="1:6">
       <c r="A83" t="s">
         <v>172</v>
       </c>
@@ -3562,7 +3579,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" customFormat="1" spans="1:6">
       <c r="A84" t="s">
         <v>174</v>
       </c>
@@ -3582,7 +3599,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" customFormat="1" spans="1:6">
       <c r="A85" t="s">
         <v>176</v>
       </c>
@@ -3602,7 +3619,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" customFormat="1" spans="1:6">
       <c r="A86" t="s">
         <v>178</v>
       </c>
@@ -3622,7 +3639,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" customFormat="1" spans="1:6">
       <c r="A87" t="s">
         <v>166</v>
       </c>
@@ -3642,7 +3659,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" customFormat="1" spans="1:6">
       <c r="A88" t="s">
         <v>181</v>
       </c>
@@ -3662,7 +3679,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" customFormat="1" spans="1:6">
       <c r="A89" t="s">
         <v>183</v>
       </c>
@@ -3682,7 +3699,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" customFormat="1" spans="1:6">
       <c r="A90" t="s">
         <v>185</v>
       </c>
@@ -3702,7 +3719,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" customFormat="1" spans="1:6">
       <c r="A91" t="s">
         <v>187</v>
       </c>
@@ -3722,7 +3739,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" customFormat="1" spans="1:6">
       <c r="A92" t="s">
         <v>189</v>
       </c>
@@ -3742,7 +3759,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" customFormat="1" spans="1:6">
       <c r="A93" t="s">
         <v>191</v>
       </c>
@@ -3762,7 +3779,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
+    <row r="94" customFormat="1" spans="1:6">
       <c r="A94" t="s">
         <v>193</v>
       </c>
@@ -3782,7 +3799,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" customFormat="1" spans="1:6">
       <c r="A95" t="s">
         <v>195</v>
       </c>
@@ -3802,7 +3819,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" customFormat="1" spans="1:6">
       <c r="A96" t="s">
         <v>197</v>
       </c>
@@ -3822,7 +3839,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" customFormat="1" spans="1:6">
       <c r="A97" t="s">
         <v>199</v>
       </c>
@@ -3842,7 +3859,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98" customFormat="1" spans="1:6">
       <c r="A98" t="s">
         <v>201</v>
       </c>
@@ -3862,7 +3879,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="99" spans="1:6">
+    <row r="99" customFormat="1" spans="1:6">
       <c r="A99" t="s">
         <v>203</v>
       </c>
@@ -3882,7 +3899,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" customFormat="1" spans="1:6">
       <c r="A100" t="s">
         <v>205</v>
       </c>
@@ -3902,7 +3919,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" customFormat="1" spans="1:6">
       <c r="A101" t="s">
         <v>207</v>
       </c>
@@ -3922,7 +3939,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" customFormat="1" spans="1:6">
       <c r="A102" t="s">
         <v>209</v>
       </c>
@@ -3942,7 +3959,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" customFormat="1" spans="1:6">
       <c r="A103" t="s">
         <v>211</v>
       </c>
@@ -3962,7 +3979,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" customFormat="1" spans="1:6">
       <c r="A104" t="s">
         <v>213</v>
       </c>
@@ -3982,7 +3999,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" customFormat="1" spans="1:6">
       <c r="A105" t="s">
         <v>215</v>
       </c>
@@ -4002,7 +4019,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" customFormat="1" spans="1:6">
       <c r="A106" t="s">
         <v>217</v>
       </c>
@@ -4022,7 +4039,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" customFormat="1" spans="1:6">
       <c r="A107" t="s">
         <v>219</v>
       </c>
@@ -4042,7 +4059,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:6">
+    <row r="108" customFormat="1" spans="1:6">
       <c r="A108" t="s">
         <v>221</v>
       </c>
@@ -4062,7 +4079,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
+    <row r="109" customFormat="1" spans="1:6">
       <c r="A109" t="s">
         <v>223</v>
       </c>
@@ -4082,7 +4099,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" customFormat="1" spans="1:6">
       <c r="A110" t="s">
         <v>225</v>
       </c>
@@ -4102,7 +4119,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" customFormat="1" spans="1:6">
       <c r="A111" t="s">
         <v>227</v>
       </c>
@@ -4122,7 +4139,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" customFormat="1" spans="1:6">
       <c r="A112" t="s">
         <v>229</v>
       </c>
@@ -4142,7 +4159,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" customFormat="1" spans="1:6">
       <c r="A113" t="s">
         <v>231</v>
       </c>
@@ -4162,7 +4179,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" customFormat="1" spans="1:6">
       <c r="A114" t="s">
         <v>233</v>
       </c>
@@ -4182,7 +4199,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
+    <row r="115" customFormat="1" spans="1:6">
       <c r="A115" t="s">
         <v>235</v>
       </c>
@@ -4202,7 +4219,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" customFormat="1" spans="1:6">
       <c r="A116" t="s">
         <v>237</v>
       </c>
@@ -4222,7 +4239,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" customFormat="1" spans="1:6">
       <c r="A117" t="s">
         <v>239</v>
       </c>
@@ -4242,7 +4259,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" customFormat="1" spans="1:6">
       <c r="A118" t="s">
         <v>241</v>
       </c>
@@ -4262,7 +4279,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" customFormat="1" spans="1:6">
       <c r="A119" t="s">
         <v>243</v>
       </c>
@@ -4282,7 +4299,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" customFormat="1" spans="1:6">
       <c r="A120" t="s">
         <v>245</v>
       </c>
@@ -4302,7 +4319,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" customFormat="1" spans="1:6">
       <c r="A121" t="s">
         <v>247</v>
       </c>
@@ -4322,7 +4339,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" customFormat="1" spans="1:6">
       <c r="A122" t="s">
         <v>249</v>
       </c>
@@ -4342,7 +4359,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="123" spans="1:6">
+    <row r="123" customFormat="1" spans="1:6">
       <c r="A123" t="s">
         <v>251</v>
       </c>
@@ -4362,7 +4379,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" customFormat="1" spans="1:6">
       <c r="A124" t="s">
         <v>253</v>
       </c>
@@ -4382,7 +4399,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="125" spans="1:6">
+    <row r="125" customFormat="1" spans="1:6">
       <c r="A125" t="s">
         <v>255</v>
       </c>
@@ -4402,7 +4419,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" customFormat="1" spans="1:6">
       <c r="A126" t="s">
         <v>257</v>
       </c>
@@ -4422,7 +4439,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" customFormat="1" spans="1:6">
       <c r="A127" t="s">
         <v>259</v>
       </c>
@@ -4442,7 +4459,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" customFormat="1" spans="1:6">
       <c r="A128" t="s">
         <v>261</v>
       </c>
@@ -4462,7 +4479,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" customFormat="1" spans="1:6">
       <c r="A129" t="s">
         <v>263</v>
       </c>
@@ -4482,7 +4499,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" customFormat="1" spans="1:6">
       <c r="A130" t="s">
         <v>265</v>
       </c>
@@ -4502,7 +4519,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="131" spans="1:6">
+    <row r="131" customFormat="1" spans="1:6">
       <c r="A131" t="s">
         <v>267</v>
       </c>
@@ -4522,7 +4539,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" customFormat="1" spans="1:6">
       <c r="A132" t="s">
         <v>269</v>
       </c>
@@ -4542,7 +4559,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="133" spans="1:6">
+    <row r="133" customFormat="1" spans="1:6">
       <c r="A133" t="s">
         <v>271</v>
       </c>
@@ -4642,15 +4659,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" customFormat="1" spans="1:6">
       <c r="A138" t="s">
         <v>282</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="C138" s="1">
-        <v>3</v>
+      <c r="C138" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>9</v>
@@ -4662,15 +4679,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" customFormat="1" spans="1:6">
       <c r="A139" t="s">
         <v>284</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C139" s="1">
-        <v>3</v>
+      <c r="C139" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>9</v>
@@ -4682,15 +4699,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" customFormat="1" spans="1:6">
       <c r="A140" t="s">
         <v>286</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="C140" s="1">
-        <v>3</v>
+      <c r="C140" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>9</v>
@@ -4702,15 +4719,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" customFormat="1" spans="1:6">
       <c r="A141" t="s">
         <v>288</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C141" s="1">
-        <v>3</v>
+      <c r="C141" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>9</v>
@@ -4722,15 +4739,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" customFormat="1" spans="1:6">
       <c r="A142" t="s">
         <v>290</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="C142" s="1">
-        <v>3</v>
+      <c r="C142" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>9</v>
@@ -4742,15 +4759,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" customFormat="1" spans="1:6">
       <c r="A143" t="s">
         <v>292</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C143" s="1">
-        <v>3</v>
+      <c r="C143" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>9</v>
@@ -4762,15 +4779,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" customFormat="1" spans="1:6">
       <c r="A144" t="s">
         <v>294</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C144" s="1">
-        <v>3</v>
+      <c r="C144" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>9</v>
@@ -4782,15 +4799,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" customFormat="1" spans="1:6">
       <c r="A145" t="s">
         <v>296</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="C145" s="1">
-        <v>3</v>
+      <c r="C145" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>9</v>
@@ -4802,15 +4819,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="146" spans="1:6">
+    <row r="146" customFormat="1" spans="1:6">
       <c r="A146" t="s">
         <v>298</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C146" s="1">
-        <v>3</v>
+      <c r="C146" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>9</v>
@@ -4822,49 +4839,143 @@
         <v>11</v>
       </c>
     </row>
-    <row r="147" spans="1:6">
+    <row r="147" customFormat="1" spans="1:6">
       <c r="A147" t="s">
+        <v>280</v>
+      </c>
+      <c r="B147" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="B147" s="2" t="s">
+      <c r="C147" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E147" t="s">
+        <v>10</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="148" customFormat="1" spans="1:6">
+      <c r="A148" t="s">
         <v>301</v>
       </c>
-      <c r="C147" s="1">
-        <v>3</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E147" t="s">
-        <v>10</v>
-      </c>
-      <c r="F147" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6">
-      <c r="A148" t="s">
+      <c r="B148" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="B148" s="2" t="s">
+      <c r="C148" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E148" t="s">
+        <v>10</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="149" customFormat="1" spans="1:6">
+      <c r="A149" t="s">
         <v>303</v>
       </c>
-      <c r="C148" s="1">
-        <v>3</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E148" t="s">
-        <v>10</v>
-      </c>
-      <c r="F148" s="1" t="s">
+      <c r="B149" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E149" t="s">
+        <v>10</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="150" customFormat="1" spans="1:6">
+      <c r="A150" t="s">
+        <v>305</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E150" t="s">
+        <v>10</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="151" customFormat="1" spans="1:6">
+      <c r="A151" t="s">
+        <v>307</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E151" t="s">
+        <v>10</v>
+      </c>
+      <c r="F151" s="1" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F148" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
+  <conditionalFormatting sqref="A35">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A69">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A74">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A75">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A80">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A70:A71">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A78:A79">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B$1:B$1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A68 A81:A1048576 A76:A77 A72:A73">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/testdata/listForExecution.xlsx
+++ b/testdata/listForExecution.xlsx
@@ -4,14 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13128" windowHeight="8232"/>
+    <workbookView windowWidth="23040" windowHeight="8340"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$148</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -30,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="304">
   <si>
     <t>TestName</t>
   </si>
@@ -878,85 +875,70 @@
     <t>C70900</t>
   </si>
   <si>
-    <t>Payments_Currency_Exchange_Pricelist_[WEB]-Overview</t>
+    <t>Payments_Domestic_Payments_Internal_Urgent_Payment_[WEB]</t>
   </si>
   <si>
     <t>C70901</t>
   </si>
   <si>
-    <t>Saving_Accounts_Transactions_Download_Option_[WEB]</t>
+    <t>Payments_Domestic_Payments_Internal_Non_Urgent_Payment_[WEB]</t>
   </si>
   <si>
     <t>C70902</t>
   </si>
   <si>
-    <t>Payments_Own_Account_Transfer_To_Loan_[WEB]</t>
+    <t>Payments_Domestic_Payments_External_Urgent_Payment_No_Model_[WEB]</t>
   </si>
   <si>
     <t>C70903</t>
   </si>
   <si>
-    <t>Payments_Own_Account_Transfer_From_Current_Foreign_Account_To_Current_Foreign_Account_[WEB]</t>
+    <t>Payments_Domestic_Payments_External_Urgent_Payment_Model11_Invalid_Bez_Poziva_Na_Broj_[WEB]</t>
   </si>
   <si>
     <t>C70904</t>
   </si>
   <si>
-    <t>Payments_Currency_Exchange_[WEB]-Buy_From_Payment</t>
+    <t>Payments_Domestic_Payments_External_Non_Urgent_Payment_Model11_[WEB]</t>
   </si>
   <si>
     <t>C70905</t>
   </si>
   <si>
-    <t>Payments_Currency_Exchange_[WEB]-Sell_From_Payment</t>
+    <t>Payments_Domestic_Payments_External_Urgent_Payment_Model97_Invalid_Bez_Poziva_Na_Broj_[WEB]</t>
   </si>
   <si>
     <t>C70906</t>
   </si>
   <si>
-    <t>Savings_Accounts_Transactions_Filter_By_Date_Date_Picker_[WEB]</t>
+    <t>Payments_Domestic_Payments_External_Non_Urgent_Payment_Model97_[WEB]</t>
   </si>
   <si>
     <t>C70907</t>
   </si>
   <si>
-    <t>Payments_Recipient_Template_List_[WEB]</t>
+    <t>Payments_Domestic_Payments_Budzetski_Urgent_Payment_Purpose_Code_289_Invalid_[WEB]</t>
   </si>
   <si>
     <t>C70908</t>
   </si>
   <si>
-    <t>Payments_Upcoming_Payments_Details_Of_Payments_Transaction_On_The_List_Of_Transaction_[WEB]</t>
+    <t>Payments_Domestic_Payments_Budzetski_Urgent_Payment_Without_Reference_Number_Invalid_[WEB]</t>
   </si>
   <si>
     <t>C70909</t>
   </si>
   <si>
+    <t>Payments_Domestic_Payments_Budzetski_Urgent_Payment_Model97_[WEB]</t>
+  </si>
+  <si>
     <t>C70910</t>
   </si>
   <si>
-    <t>Payments_Payments_Archive_Payments_Details_[WEB]</t>
+    <t>Payments_Domestic_Payments_Budzetski_Non_Urgent_Payment_Model97_[WEB]</t>
   </si>
   <si>
     <t>C70911</t>
-  </si>
-  <si>
-    <t>Current_Accounts_RSD_Statemants_List_[WEB]</t>
-  </si>
-  <si>
-    <t>C70912</t>
-  </si>
-  <si>
-    <t>Current_Foreign_Accounts_Statemants_List_[WEB]</t>
-  </si>
-  <si>
-    <t>C70913</t>
-  </si>
-  <si>
-    <t>Saving_Accounts_Accounts_Statemants_List_[WEB]</t>
-  </si>
-  <si>
-    <t>C70914</t>
   </si>
 </sst>
 </file>
@@ -1913,13 +1895,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F151"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <dimension ref="A1:F148"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="91.1388888888889" customWidth="1"/>
+    <col min="1" max="1" width="94.1428571428571" customWidth="1"/>
+    <col min="2" max="2" width="11.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:6">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1959,7 +1942,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" customFormat="1" spans="1:6">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1979,7 +1962,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" customFormat="1" spans="1:6">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1999,7 +1982,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="1:6">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -2019,7 +2002,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="1:6">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -2039,7 +2022,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" customFormat="1" spans="1:6">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -2059,7 +2042,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" customFormat="1" spans="1:6">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -2079,7 +2062,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" customFormat="1" spans="1:6">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -2099,7 +2082,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" customFormat="1" spans="1:6">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -2119,7 +2102,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" customFormat="1" spans="1:6">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -2139,7 +2122,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" customFormat="1" spans="1:6">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -2159,7 +2142,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" customFormat="1" spans="1:6">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -2179,7 +2162,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" customFormat="1" spans="1:6">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -2199,7 +2182,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" customFormat="1" spans="1:6">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -2219,7 +2202,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" customFormat="1" spans="1:6">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -2239,7 +2222,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" customFormat="1" spans="1:6">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -2259,7 +2242,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" customFormat="1" spans="1:6">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -2279,7 +2262,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" customFormat="1" spans="1:6">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -2299,7 +2282,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" customFormat="1" spans="1:6">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>46</v>
       </c>
@@ -2319,7 +2302,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" customFormat="1" spans="1:6">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>48</v>
       </c>
@@ -2339,7 +2322,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" customFormat="1" spans="1:6">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -2359,7 +2342,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" customFormat="1" spans="1:6">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>52</v>
       </c>
@@ -2379,7 +2362,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" customFormat="1" spans="1:6">
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -2399,7 +2382,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" customFormat="1" spans="1:6">
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -2419,7 +2402,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" customFormat="1" spans="1:6">
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -2439,7 +2422,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" customFormat="1" spans="1:6">
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
         <v>60</v>
       </c>
@@ -2459,7 +2442,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" customFormat="1" spans="1:6">
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>62</v>
       </c>
@@ -2479,7 +2462,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" customFormat="1" spans="1:6">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>64</v>
       </c>
@@ -2499,7 +2482,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" customFormat="1" spans="1:6">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>66</v>
       </c>
@@ -2519,7 +2502,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" customFormat="1" spans="1:6">
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
         <v>68</v>
       </c>
@@ -2539,7 +2522,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" customFormat="1" spans="1:6">
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
         <v>70</v>
       </c>
@@ -2559,7 +2542,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="33" customFormat="1" spans="1:6">
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
         <v>72</v>
       </c>
@@ -2579,7 +2562,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" customFormat="1" spans="1:6">
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
         <v>74</v>
       </c>
@@ -2599,7 +2582,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" customFormat="1" spans="1:6">
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
         <v>76</v>
       </c>
@@ -2619,7 +2602,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="36" customFormat="1" spans="1:6">
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
         <v>78</v>
       </c>
@@ -2639,7 +2622,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" customFormat="1" spans="1:6">
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
         <v>80</v>
       </c>
@@ -2659,7 +2642,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" customFormat="1" spans="1:6">
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
         <v>82</v>
       </c>
@@ -2679,7 +2662,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" customFormat="1" spans="1:6">
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
         <v>84</v>
       </c>
@@ -2699,7 +2682,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" customFormat="1" spans="1:6">
+    <row r="40" spans="1:6">
       <c r="A40" t="s">
         <v>86</v>
       </c>
@@ -2719,7 +2702,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" customFormat="1" spans="1:6">
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
         <v>88</v>
       </c>
@@ -2739,7 +2722,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" customFormat="1" spans="1:6">
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
         <v>90</v>
       </c>
@@ -2759,7 +2742,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" customFormat="1" spans="1:6">
+    <row r="43" spans="1:6">
       <c r="A43" t="s">
         <v>92</v>
       </c>
@@ -2779,7 +2762,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" customFormat="1" spans="1:6">
+    <row r="44" spans="1:6">
       <c r="A44" t="s">
         <v>94</v>
       </c>
@@ -2799,7 +2782,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" customFormat="1" spans="1:6">
+    <row r="45" spans="1:6">
       <c r="A45" t="s">
         <v>96</v>
       </c>
@@ -2819,7 +2802,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="46" customFormat="1" spans="1:6">
+    <row r="46" spans="1:6">
       <c r="A46" t="s">
         <v>98</v>
       </c>
@@ -2839,7 +2822,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" customFormat="1" spans="1:6">
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
         <v>100</v>
       </c>
@@ -2859,7 +2842,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48" customFormat="1" spans="1:6">
+    <row r="48" spans="1:6">
       <c r="A48" t="s">
         <v>102</v>
       </c>
@@ -2879,7 +2862,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" customFormat="1" spans="1:6">
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
         <v>104</v>
       </c>
@@ -2899,7 +2882,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" customFormat="1" spans="1:6">
+    <row r="50" spans="1:6">
       <c r="A50" t="s">
         <v>106</v>
       </c>
@@ -2919,7 +2902,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" customFormat="1" spans="1:6">
+    <row r="51" spans="1:6">
       <c r="A51" t="s">
         <v>108</v>
       </c>
@@ -2939,7 +2922,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" customFormat="1" spans="1:6">
+    <row r="52" spans="1:6">
       <c r="A52" t="s">
         <v>110</v>
       </c>
@@ -2959,7 +2942,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" customFormat="1" spans="1:6">
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
         <v>112</v>
       </c>
@@ -2979,7 +2962,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" customFormat="1" spans="1:6">
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
         <v>114</v>
       </c>
@@ -2999,7 +2982,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="55" customFormat="1" spans="1:6">
+    <row r="55" spans="1:6">
       <c r="A55" t="s">
         <v>116</v>
       </c>
@@ -3019,7 +3002,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="56" customFormat="1" spans="1:6">
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
         <v>118</v>
       </c>
@@ -3039,7 +3022,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="57" customFormat="1" spans="1:6">
+    <row r="57" spans="1:6">
       <c r="A57" t="s">
         <v>120</v>
       </c>
@@ -3059,7 +3042,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="58" customFormat="1" spans="1:6">
+    <row r="58" spans="1:6">
       <c r="A58" t="s">
         <v>122</v>
       </c>
@@ -3079,7 +3062,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" customFormat="1" spans="1:6">
+    <row r="59" spans="1:6">
       <c r="A59" t="s">
         <v>124</v>
       </c>
@@ -3099,7 +3082,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="60" customFormat="1" spans="1:6">
+    <row r="60" spans="1:6">
       <c r="A60" t="s">
         <v>126</v>
       </c>
@@ -3119,7 +3102,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" customFormat="1" spans="1:6">
+    <row r="61" spans="1:6">
       <c r="A61" t="s">
         <v>128</v>
       </c>
@@ -3139,7 +3122,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="62" customFormat="1" spans="1:6">
+    <row r="62" spans="1:6">
       <c r="A62" t="s">
         <v>130</v>
       </c>
@@ -3159,7 +3142,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="63" customFormat="1" spans="1:6">
+    <row r="63" spans="1:6">
       <c r="A63" t="s">
         <v>132</v>
       </c>
@@ -3179,7 +3162,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="64" customFormat="1" spans="1:6">
+    <row r="64" spans="1:6">
       <c r="A64" t="s">
         <v>134</v>
       </c>
@@ -3199,7 +3182,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="65" customFormat="1" spans="1:6">
+    <row r="65" spans="1:6">
       <c r="A65" t="s">
         <v>136</v>
       </c>
@@ -3219,7 +3202,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="66" customFormat="1" spans="1:6">
+    <row r="66" spans="1:6">
       <c r="A66" t="s">
         <v>138</v>
       </c>
@@ -3239,7 +3222,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" customFormat="1" spans="1:6">
+    <row r="67" spans="1:6">
       <c r="A67" t="s">
         <v>140</v>
       </c>
@@ -3259,7 +3242,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="68" customFormat="1" spans="1:6">
+    <row r="68" spans="1:6">
       <c r="A68" t="s">
         <v>142</v>
       </c>
@@ -3279,7 +3262,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="69" customFormat="1" spans="1:6">
+    <row r="69" spans="1:6">
       <c r="A69" t="s">
         <v>144</v>
       </c>
@@ -3299,7 +3282,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="70" customFormat="1" spans="1:6">
+    <row r="70" spans="1:6">
       <c r="A70" t="s">
         <v>146</v>
       </c>
@@ -3319,7 +3302,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="71" customFormat="1" spans="1:6">
+    <row r="71" spans="1:6">
       <c r="A71" t="s">
         <v>148</v>
       </c>
@@ -3339,7 +3322,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="72" customFormat="1" spans="1:6">
+    <row r="72" spans="1:6">
       <c r="A72" t="s">
         <v>150</v>
       </c>
@@ -3359,7 +3342,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="73" customFormat="1" spans="1:6">
+    <row r="73" spans="1:6">
       <c r="A73" t="s">
         <v>152</v>
       </c>
@@ -3379,7 +3362,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" customFormat="1" spans="1:6">
+    <row r="74" spans="1:6">
       <c r="A74" t="s">
         <v>154</v>
       </c>
@@ -3399,7 +3382,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" customFormat="1" spans="1:6">
+    <row r="75" spans="1:6">
       <c r="A75" t="s">
         <v>156</v>
       </c>
@@ -3419,7 +3402,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" customFormat="1" spans="1:6">
+    <row r="76" spans="1:6">
       <c r="A76" t="s">
         <v>158</v>
       </c>
@@ -3439,7 +3422,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="77" customFormat="1" spans="1:6">
+    <row r="77" spans="1:6">
       <c r="A77" t="s">
         <v>160</v>
       </c>
@@ -3459,7 +3442,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="78" customFormat="1" spans="1:6">
+    <row r="78" spans="1:6">
       <c r="A78" t="s">
         <v>162</v>
       </c>
@@ -3479,7 +3462,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="79" customFormat="1" spans="1:6">
+    <row r="79" spans="1:6">
       <c r="A79" t="s">
         <v>164</v>
       </c>
@@ -3499,7 +3482,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="80" customFormat="1" spans="1:6">
+    <row r="80" spans="1:6">
       <c r="A80" t="s">
         <v>166</v>
       </c>
@@ -3519,7 +3502,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="81" customFormat="1" spans="1:6">
+    <row r="81" spans="1:6">
       <c r="A81" t="s">
         <v>168</v>
       </c>
@@ -3539,7 +3522,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" customFormat="1" spans="1:6">
+    <row r="82" spans="1:6">
       <c r="A82" t="s">
         <v>170</v>
       </c>
@@ -3559,7 +3542,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="83" customFormat="1" spans="1:6">
+    <row r="83" spans="1:6">
       <c r="A83" t="s">
         <v>172</v>
       </c>
@@ -3579,7 +3562,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="84" customFormat="1" spans="1:6">
+    <row r="84" spans="1:6">
       <c r="A84" t="s">
         <v>174</v>
       </c>
@@ -3599,7 +3582,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="85" customFormat="1" spans="1:6">
+    <row r="85" spans="1:6">
       <c r="A85" t="s">
         <v>176</v>
       </c>
@@ -3619,7 +3602,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="86" customFormat="1" spans="1:6">
+    <row r="86" spans="1:6">
       <c r="A86" t="s">
         <v>178</v>
       </c>
@@ -3639,7 +3622,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="87" customFormat="1" spans="1:6">
+    <row r="87" spans="1:6">
       <c r="A87" t="s">
         <v>166</v>
       </c>
@@ -3659,7 +3642,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="88" customFormat="1" spans="1:6">
+    <row r="88" spans="1:6">
       <c r="A88" t="s">
         <v>181</v>
       </c>
@@ -3679,7 +3662,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="89" customFormat="1" spans="1:6">
+    <row r="89" spans="1:6">
       <c r="A89" t="s">
         <v>183</v>
       </c>
@@ -3699,7 +3682,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="90" customFormat="1" spans="1:6">
+    <row r="90" spans="1:6">
       <c r="A90" t="s">
         <v>185</v>
       </c>
@@ -3719,7 +3702,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="91" customFormat="1" spans="1:6">
+    <row r="91" spans="1:6">
       <c r="A91" t="s">
         <v>187</v>
       </c>
@@ -3739,7 +3722,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" customFormat="1" spans="1:6">
+    <row r="92" spans="1:6">
       <c r="A92" t="s">
         <v>189</v>
       </c>
@@ -3759,7 +3742,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="93" customFormat="1" spans="1:6">
+    <row r="93" spans="1:6">
       <c r="A93" t="s">
         <v>191</v>
       </c>
@@ -3779,7 +3762,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="94" customFormat="1" spans="1:6">
+    <row r="94" spans="1:6">
       <c r="A94" t="s">
         <v>193</v>
       </c>
@@ -3799,7 +3782,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="95" customFormat="1" spans="1:6">
+    <row r="95" spans="1:6">
       <c r="A95" t="s">
         <v>195</v>
       </c>
@@ -3819,7 +3802,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="96" customFormat="1" spans="1:6">
+    <row r="96" spans="1:6">
       <c r="A96" t="s">
         <v>197</v>
       </c>
@@ -3839,7 +3822,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="97" customFormat="1" spans="1:6">
+    <row r="97" spans="1:6">
       <c r="A97" t="s">
         <v>199</v>
       </c>
@@ -3859,7 +3842,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="98" customFormat="1" spans="1:6">
+    <row r="98" spans="1:6">
       <c r="A98" t="s">
         <v>201</v>
       </c>
@@ -3879,7 +3862,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="99" customFormat="1" spans="1:6">
+    <row r="99" spans="1:6">
       <c r="A99" t="s">
         <v>203</v>
       </c>
@@ -3899,7 +3882,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="100" customFormat="1" spans="1:6">
+    <row r="100" spans="1:6">
       <c r="A100" t="s">
         <v>205</v>
       </c>
@@ -3919,7 +3902,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="101" customFormat="1" spans="1:6">
+    <row r="101" spans="1:6">
       <c r="A101" t="s">
         <v>207</v>
       </c>
@@ -3939,7 +3922,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="102" customFormat="1" spans="1:6">
+    <row r="102" spans="1:6">
       <c r="A102" t="s">
         <v>209</v>
       </c>
@@ -3959,7 +3942,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="103" customFormat="1" spans="1:6">
+    <row r="103" spans="1:6">
       <c r="A103" t="s">
         <v>211</v>
       </c>
@@ -3979,7 +3962,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="104" customFormat="1" spans="1:6">
+    <row r="104" spans="1:6">
       <c r="A104" t="s">
         <v>213</v>
       </c>
@@ -3999,7 +3982,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="105" customFormat="1" spans="1:6">
+    <row r="105" spans="1:6">
       <c r="A105" t="s">
         <v>215</v>
       </c>
@@ -4019,7 +4002,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="106" customFormat="1" spans="1:6">
+    <row r="106" spans="1:6">
       <c r="A106" t="s">
         <v>217</v>
       </c>
@@ -4039,7 +4022,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="107" customFormat="1" spans="1:6">
+    <row r="107" spans="1:6">
       <c r="A107" t="s">
         <v>219</v>
       </c>
@@ -4059,7 +4042,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="108" customFormat="1" spans="1:6">
+    <row r="108" spans="1:6">
       <c r="A108" t="s">
         <v>221</v>
       </c>
@@ -4079,7 +4062,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="109" customFormat="1" spans="1:6">
+    <row r="109" spans="1:6">
       <c r="A109" t="s">
         <v>223</v>
       </c>
@@ -4099,7 +4082,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="110" customFormat="1" spans="1:6">
+    <row r="110" spans="1:6">
       <c r="A110" t="s">
         <v>225</v>
       </c>
@@ -4119,7 +4102,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="111" customFormat="1" spans="1:6">
+    <row r="111" spans="1:6">
       <c r="A111" t="s">
         <v>227</v>
       </c>
@@ -4139,7 +4122,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" customFormat="1" spans="1:6">
+    <row r="112" spans="1:6">
       <c r="A112" t="s">
         <v>229</v>
       </c>
@@ -4159,7 +4142,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="113" customFormat="1" spans="1:6">
+    <row r="113" spans="1:6">
       <c r="A113" t="s">
         <v>231</v>
       </c>
@@ -4179,7 +4162,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="114" customFormat="1" spans="1:6">
+    <row r="114" spans="1:6">
       <c r="A114" t="s">
         <v>233</v>
       </c>
@@ -4199,7 +4182,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" customFormat="1" spans="1:6">
+    <row r="115" spans="1:6">
       <c r="A115" t="s">
         <v>235</v>
       </c>
@@ -4219,7 +4202,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="116" customFormat="1" spans="1:6">
+    <row r="116" spans="1:6">
       <c r="A116" t="s">
         <v>237</v>
       </c>
@@ -4239,7 +4222,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="117" customFormat="1" spans="1:6">
+    <row r="117" spans="1:6">
       <c r="A117" t="s">
         <v>239</v>
       </c>
@@ -4259,7 +4242,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="118" customFormat="1" spans="1:6">
+    <row r="118" spans="1:6">
       <c r="A118" t="s">
         <v>241</v>
       </c>
@@ -4279,7 +4262,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="119" customFormat="1" spans="1:6">
+    <row r="119" spans="1:6">
       <c r="A119" t="s">
         <v>243</v>
       </c>
@@ -4299,7 +4282,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="120" customFormat="1" spans="1:6">
+    <row r="120" spans="1:6">
       <c r="A120" t="s">
         <v>245</v>
       </c>
@@ -4319,7 +4302,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="121" customFormat="1" spans="1:6">
+    <row r="121" spans="1:6">
       <c r="A121" t="s">
         <v>247</v>
       </c>
@@ -4339,7 +4322,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="122" customFormat="1" spans="1:6">
+    <row r="122" spans="1:6">
       <c r="A122" t="s">
         <v>249</v>
       </c>
@@ -4359,7 +4342,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="123" customFormat="1" spans="1:6">
+    <row r="123" spans="1:6">
       <c r="A123" t="s">
         <v>251</v>
       </c>
@@ -4379,7 +4362,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="124" customFormat="1" spans="1:6">
+    <row r="124" spans="1:6">
       <c r="A124" t="s">
         <v>253</v>
       </c>
@@ -4399,7 +4382,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="125" customFormat="1" spans="1:6">
+    <row r="125" spans="1:6">
       <c r="A125" t="s">
         <v>255</v>
       </c>
@@ -4419,7 +4402,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="126" customFormat="1" spans="1:6">
+    <row r="126" spans="1:6">
       <c r="A126" t="s">
         <v>257</v>
       </c>
@@ -4439,7 +4422,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" customFormat="1" spans="1:6">
+    <row r="127" spans="1:6">
       <c r="A127" t="s">
         <v>259</v>
       </c>
@@ -4459,7 +4442,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="128" customFormat="1" spans="1:6">
+    <row r="128" spans="1:6">
       <c r="A128" t="s">
         <v>261</v>
       </c>
@@ -4479,7 +4462,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="129" customFormat="1" spans="1:6">
+    <row r="129" spans="1:6">
       <c r="A129" t="s">
         <v>263</v>
       </c>
@@ -4499,7 +4482,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" customFormat="1" spans="1:6">
+    <row r="130" spans="1:6">
       <c r="A130" t="s">
         <v>265</v>
       </c>
@@ -4519,7 +4502,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="131" customFormat="1" spans="1:6">
+    <row r="131" spans="1:6">
       <c r="A131" t="s">
         <v>267</v>
       </c>
@@ -4539,7 +4522,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="132" customFormat="1" spans="1:6">
+    <row r="132" spans="1:6">
       <c r="A132" t="s">
         <v>269</v>
       </c>
@@ -4559,7 +4542,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="133" customFormat="1" spans="1:6">
+    <row r="133" spans="1:6">
       <c r="A133" t="s">
         <v>271</v>
       </c>
@@ -4659,15 +4642,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="138" customFormat="1" spans="1:6">
+    <row r="138" spans="1:6">
       <c r="A138" t="s">
         <v>282</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="C138" s="1" t="s">
-        <v>8</v>
+      <c r="C138" s="1">
+        <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>9</v>
@@ -4679,15 +4662,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="139" customFormat="1" spans="1:6">
+    <row r="139" spans="1:6">
       <c r="A139" t="s">
         <v>284</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C139" s="1" t="s">
-        <v>8</v>
+      <c r="C139" s="1">
+        <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>9</v>
@@ -4699,15 +4682,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="140" customFormat="1" spans="1:6">
+    <row r="140" spans="1:6">
       <c r="A140" t="s">
         <v>286</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="C140" s="1" t="s">
-        <v>8</v>
+      <c r="C140" s="1">
+        <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>9</v>
@@ -4719,15 +4702,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="141" customFormat="1" spans="1:6">
+    <row r="141" spans="1:6">
       <c r="A141" t="s">
         <v>288</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C141" s="1" t="s">
-        <v>8</v>
+      <c r="C141" s="1">
+        <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>9</v>
@@ -4739,15 +4722,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="142" customFormat="1" spans="1:6">
+    <row r="142" spans="1:6">
       <c r="A142" t="s">
         <v>290</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="C142" s="1" t="s">
-        <v>8</v>
+      <c r="C142" s="1">
+        <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>9</v>
@@ -4759,15 +4742,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="143" customFormat="1" spans="1:6">
+    <row r="143" spans="1:6">
       <c r="A143" t="s">
         <v>292</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C143" s="1" t="s">
-        <v>8</v>
+      <c r="C143" s="1">
+        <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>9</v>
@@ -4779,15 +4762,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="144" customFormat="1" spans="1:6">
+    <row r="144" spans="1:6">
       <c r="A144" t="s">
         <v>294</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C144" s="1" t="s">
-        <v>8</v>
+      <c r="C144" s="1">
+        <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>9</v>
@@ -4799,15 +4782,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="145" customFormat="1" spans="1:6">
+    <row r="145" spans="1:6">
       <c r="A145" t="s">
         <v>296</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="C145" s="1" t="s">
-        <v>8</v>
+      <c r="C145" s="1">
+        <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>9</v>
@@ -4819,15 +4802,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="146" customFormat="1" spans="1:6">
+    <row r="146" spans="1:6">
       <c r="A146" t="s">
         <v>298</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C146" s="1" t="s">
-        <v>8</v>
+      <c r="C146" s="1">
+        <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>9</v>
@@ -4839,15 +4822,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="147" customFormat="1" spans="1:6">
+    <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>8</v>
+        <v>301</v>
+      </c>
+      <c r="C147" s="1">
+        <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>9</v>
@@ -4859,15 +4842,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="148" customFormat="1" spans="1:6">
+    <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>8</v>
+        <v>303</v>
+      </c>
+      <c r="C148" s="1">
+        <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>9</v>
@@ -4879,103 +4862,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="149" customFormat="1" spans="1:6">
-      <c r="A149" t="s">
-        <v>303</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E149" t="s">
-        <v>10</v>
-      </c>
-      <c r="F149" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="150" customFormat="1" spans="1:6">
-      <c r="A150" t="s">
-        <v>305</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C150" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E150" t="s">
-        <v>10</v>
-      </c>
-      <c r="F150" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="151" customFormat="1" spans="1:6">
-      <c r="A151" t="s">
-        <v>307</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="C151" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E151" t="s">
-        <v>10</v>
-      </c>
-      <c r="F151" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F148" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
-  <conditionalFormatting sqref="A35">
-    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A69">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A74">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A75">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A80">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  <conditionalFormatting sqref="B$1:B$1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A70:A71">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A78:A79">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B$1:B$1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A68 A81:A1048576 A76:A77 A72:A73">
-    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/testdata/listForExecution.xlsx
+++ b/testdata/listForExecution.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="310">
   <si>
     <t>TestName</t>
   </si>
@@ -939,6 +939,24 @@
   </si>
   <si>
     <t>C70911</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Urgent_Payment_Model97_[WEB]</t>
+  </si>
+  <si>
+    <t>C70912</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Urgent_Payment_Model11_[WEB]</t>
+  </si>
+  <si>
+    <t>C70913</t>
+  </si>
+  <si>
+    <t>Payments_Domestic_Payments_External_Non_Urgent_Payment_No_Model_[WEB]</t>
+  </si>
+  <si>
+    <t>C70914</t>
   </si>
 </sst>
 </file>
@@ -1895,7 +1913,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F148"/>
+  <dimension ref="A1:F151"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="94.1428571428571" customWidth="1"/>
@@ -4862,6 +4880,66 @@
         <v>11</v>
       </c>
     </row>
+    <row r="149" spans="1:6">
+      <c r="A149" t="s">
+        <v>304</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C149" s="1">
+        <v>3</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E149" t="s">
+        <v>10</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6">
+      <c r="A150" t="s">
+        <v>306</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C150" s="1">
+        <v>3</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E150" t="s">
+        <v>10</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
+      <c r="A151" t="s">
+        <v>308</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C151" s="1">
+        <v>3</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E151" t="s">
+        <v>10</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B$1:B$1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/testdata/listForExecution.xlsx
+++ b/testdata/listForExecution.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$151</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="911" uniqueCount="312">
   <si>
     <t>TestName</t>
   </si>
@@ -957,6 +960,12 @@
   </si>
   <si>
     <t>C70914</t>
+  </si>
+  <si>
+    <t>Payments_Recipient_Last_5_Payments_Of_Recipient_[WEB]-View_And_Repeat</t>
+  </si>
+  <si>
+    <t>C70915</t>
   </si>
 </sst>
 </file>
@@ -1576,12 +1585,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1913,11 +1928,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F151"/>
+  <dimension ref="A1:F152"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="94.1428571428571" customWidth="1"/>
     <col min="2" max="2" width="11.7142857142857" customWidth="1"/>
+    <col min="3" max="3" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1927,7 +1943,7 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -1944,10 +1960,10 @@
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -1964,10 +1980,10 @@
       <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -1984,10 +2000,10 @@
       <c r="A4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -2004,10 +2020,10 @@
       <c r="A5" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -2024,10 +2040,10 @@
       <c r="A6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -2044,10 +2060,10 @@
       <c r="A7" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -2064,10 +2080,10 @@
       <c r="A8" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -2084,10 +2100,10 @@
       <c r="A9" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -2104,10 +2120,10 @@
       <c r="A10" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -2124,10 +2140,10 @@
       <c r="A11" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -2144,10 +2160,10 @@
       <c r="A12" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -2164,10 +2180,10 @@
       <c r="A13" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
@@ -2184,10 +2200,10 @@
       <c r="A14" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -2204,10 +2220,10 @@
       <c r="A15" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="1" t="s">
@@ -2224,10 +2240,10 @@
       <c r="A16" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -2244,10 +2260,10 @@
       <c r="A17" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="1" t="s">
@@ -2264,10 +2280,10 @@
       <c r="A18" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D18" s="1" t="s">
@@ -2284,10 +2300,10 @@
       <c r="A19" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D19" s="1" t="s">
@@ -2304,10 +2320,10 @@
       <c r="A20" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D20" s="1" t="s">
@@ -2324,10 +2340,10 @@
       <c r="A21" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D21" s="1" t="s">
@@ -2344,10 +2360,10 @@
       <c r="A22" t="s">
         <v>50</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D22" s="1" t="s">
@@ -2364,10 +2380,10 @@
       <c r="A23" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D23" s="1" t="s">
@@ -2384,10 +2400,10 @@
       <c r="A24" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B24" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="1" t="s">
@@ -2404,10 +2420,10 @@
       <c r="A25" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="1" t="s">
@@ -2424,10 +2440,10 @@
       <c r="A26" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D26" s="1" t="s">
@@ -2444,10 +2460,10 @@
       <c r="A27" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="1" t="s">
@@ -2464,10 +2480,10 @@
       <c r="A28" t="s">
         <v>62</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="1" t="s">
@@ -2484,10 +2500,10 @@
       <c r="A29" t="s">
         <v>64</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D29" s="1" t="s">
@@ -2504,10 +2520,10 @@
       <c r="A30" t="s">
         <v>66</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D30" s="1" t="s">
@@ -2524,10 +2540,10 @@
       <c r="A31" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D31" s="1" t="s">
@@ -2544,10 +2560,10 @@
       <c r="A32" t="s">
         <v>70</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D32" s="1" t="s">
@@ -2564,10 +2580,10 @@
       <c r="A33" t="s">
         <v>72</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D33" s="1" t="s">
@@ -2584,10 +2600,10 @@
       <c r="A34" t="s">
         <v>74</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D34" s="1" t="s">
@@ -2604,10 +2620,10 @@
       <c r="A35" t="s">
         <v>76</v>
       </c>
-      <c r="B35" s="2" t="s">
+      <c r="B35" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D35" s="1" t="s">
@@ -2624,10 +2640,10 @@
       <c r="A36" t="s">
         <v>78</v>
       </c>
-      <c r="B36" s="2" t="s">
+      <c r="B36" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D36" s="1" t="s">
@@ -2644,10 +2660,10 @@
       <c r="A37" t="s">
         <v>80</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D37" s="1" t="s">
@@ -2664,10 +2680,10 @@
       <c r="A38" t="s">
         <v>82</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D38" s="1" t="s">
@@ -2684,10 +2700,10 @@
       <c r="A39" t="s">
         <v>84</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D39" s="1" t="s">
@@ -2704,10 +2720,10 @@
       <c r="A40" t="s">
         <v>86</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D40" s="1" t="s">
@@ -2724,10 +2740,10 @@
       <c r="A41" t="s">
         <v>88</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D41" s="1" t="s">
@@ -2744,10 +2760,10 @@
       <c r="A42" t="s">
         <v>90</v>
       </c>
-      <c r="B42" s="2" t="s">
+      <c r="B42" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D42" s="1" t="s">
@@ -2764,10 +2780,10 @@
       <c r="A43" t="s">
         <v>92</v>
       </c>
-      <c r="B43" s="2" t="s">
+      <c r="B43" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D43" s="1" t="s">
@@ -2784,10 +2800,10 @@
       <c r="A44" t="s">
         <v>94</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="B44" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="1" t="s">
@@ -2804,10 +2820,10 @@
       <c r="A45" t="s">
         <v>96</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D45" s="1" t="s">
@@ -2824,10 +2840,10 @@
       <c r="A46" t="s">
         <v>98</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D46" s="1" t="s">
@@ -2844,10 +2860,10 @@
       <c r="A47" t="s">
         <v>100</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D47" s="1" t="s">
@@ -2864,10 +2880,10 @@
       <c r="A48" t="s">
         <v>102</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D48" s="1" t="s">
@@ -2884,10 +2900,10 @@
       <c r="A49" t="s">
         <v>104</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D49" s="1" t="s">
@@ -2904,10 +2920,10 @@
       <c r="A50" t="s">
         <v>106</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D50" s="1" t="s">
@@ -2924,10 +2940,10 @@
       <c r="A51" t="s">
         <v>108</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D51" s="1" t="s">
@@ -2944,10 +2960,10 @@
       <c r="A52" t="s">
         <v>110</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D52" s="1" t="s">
@@ -2964,10 +2980,10 @@
       <c r="A53" t="s">
         <v>112</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D53" s="1" t="s">
@@ -2984,10 +3000,10 @@
       <c r="A54" t="s">
         <v>114</v>
       </c>
-      <c r="B54" s="2" t="s">
+      <c r="B54" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D54" s="1" t="s">
@@ -3004,10 +3020,10 @@
       <c r="A55" t="s">
         <v>116</v>
       </c>
-      <c r="B55" s="2" t="s">
+      <c r="B55" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D55" s="1" t="s">
@@ -3024,10 +3040,10 @@
       <c r="A56" t="s">
         <v>118</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="B56" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D56" s="1" t="s">
@@ -3044,10 +3060,10 @@
       <c r="A57" t="s">
         <v>120</v>
       </c>
-      <c r="B57" s="2" t="s">
+      <c r="B57" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D57" s="1" t="s">
@@ -3064,10 +3080,10 @@
       <c r="A58" t="s">
         <v>122</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B58" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D58" s="1" t="s">
@@ -3084,10 +3100,10 @@
       <c r="A59" t="s">
         <v>124</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B59" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D59" s="1" t="s">
@@ -3104,10 +3120,10 @@
       <c r="A60" t="s">
         <v>126</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D60" s="1" t="s">
@@ -3124,10 +3140,10 @@
       <c r="A61" t="s">
         <v>128</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D61" s="1" t="s">
@@ -3144,10 +3160,10 @@
       <c r="A62" t="s">
         <v>130</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D62" s="1" t="s">
@@ -3164,10 +3180,10 @@
       <c r="A63" t="s">
         <v>132</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D63" s="1" t="s">
@@ -3184,10 +3200,10 @@
       <c r="A64" t="s">
         <v>134</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D64" s="1" t="s">
@@ -3204,10 +3220,10 @@
       <c r="A65" t="s">
         <v>136</v>
       </c>
-      <c r="B65" s="2" t="s">
+      <c r="B65" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D65" s="1" t="s">
@@ -3224,10 +3240,10 @@
       <c r="A66" t="s">
         <v>138</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B66" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D66" s="1" t="s">
@@ -3244,10 +3260,10 @@
       <c r="A67" t="s">
         <v>140</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="B67" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D67" s="1" t="s">
@@ -3264,10 +3280,10 @@
       <c r="A68" t="s">
         <v>142</v>
       </c>
-      <c r="B68" s="2" t="s">
+      <c r="B68" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D68" s="1" t="s">
@@ -3284,10 +3300,10 @@
       <c r="A69" t="s">
         <v>144</v>
       </c>
-      <c r="B69" s="2" t="s">
+      <c r="B69" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D69" s="1" t="s">
@@ -3304,10 +3320,10 @@
       <c r="A70" t="s">
         <v>146</v>
       </c>
-      <c r="B70" s="2" t="s">
+      <c r="B70" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D70" s="1" t="s">
@@ -3324,10 +3340,10 @@
       <c r="A71" t="s">
         <v>148</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B71" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C71" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D71" s="1" t="s">
@@ -3344,10 +3360,10 @@
       <c r="A72" t="s">
         <v>150</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B72" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C72" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D72" s="1" t="s">
@@ -3364,10 +3380,10 @@
       <c r="A73" t="s">
         <v>152</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B73" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C73" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D73" s="1" t="s">
@@ -3384,10 +3400,10 @@
       <c r="A74" t="s">
         <v>154</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B74" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C74" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D74" s="1" t="s">
@@ -3404,10 +3420,10 @@
       <c r="A75" t="s">
         <v>156</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B75" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C75" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D75" s="1" t="s">
@@ -3424,10 +3440,10 @@
       <c r="A76" t="s">
         <v>158</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B76" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C76" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D76" s="1" t="s">
@@ -3444,10 +3460,10 @@
       <c r="A77" t="s">
         <v>160</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B77" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C77" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D77" s="1" t="s">
@@ -3464,10 +3480,10 @@
       <c r="A78" t="s">
         <v>162</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="B78" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C78" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D78" s="1" t="s">
@@ -3484,10 +3500,10 @@
       <c r="A79" t="s">
         <v>164</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="B79" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C79" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D79" s="1" t="s">
@@ -3504,10 +3520,10 @@
       <c r="A80" t="s">
         <v>166</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B80" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C80" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D80" s="1" t="s">
@@ -3524,10 +3540,10 @@
       <c r="A81" t="s">
         <v>168</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="B81" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C81" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D81" s="1" t="s">
@@ -3544,10 +3560,10 @@
       <c r="A82" t="s">
         <v>170</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="B82" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C82" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D82" s="1" t="s">
@@ -3564,10 +3580,10 @@
       <c r="A83" t="s">
         <v>172</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="B83" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C83" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D83" s="1" t="s">
@@ -3584,10 +3600,10 @@
       <c r="A84" t="s">
         <v>174</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="B84" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C84" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D84" s="1" t="s">
@@ -3604,10 +3620,10 @@
       <c r="A85" t="s">
         <v>176</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="B85" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C85" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D85" s="1" t="s">
@@ -3624,10 +3640,10 @@
       <c r="A86" t="s">
         <v>178</v>
       </c>
-      <c r="B86" s="2" t="s">
+      <c r="B86" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C86" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D86" s="1" t="s">
@@ -3644,10 +3660,10 @@
       <c r="A87" t="s">
         <v>166</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="B87" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C87" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D87" s="1" t="s">
@@ -3664,10 +3680,10 @@
       <c r="A88" t="s">
         <v>181</v>
       </c>
-      <c r="B88" s="2" t="s">
+      <c r="B88" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C88" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D88" s="1" t="s">
@@ -3684,10 +3700,10 @@
       <c r="A89" t="s">
         <v>183</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="B89" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C89" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D89" s="1" t="s">
@@ -3704,10 +3720,10 @@
       <c r="A90" t="s">
         <v>185</v>
       </c>
-      <c r="B90" s="2" t="s">
+      <c r="B90" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C90" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D90" s="1" t="s">
@@ -3724,10 +3740,10 @@
       <c r="A91" t="s">
         <v>187</v>
       </c>
-      <c r="B91" s="2" t="s">
+      <c r="B91" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C91" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D91" s="1" t="s">
@@ -3744,10 +3760,10 @@
       <c r="A92" t="s">
         <v>189</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="B92" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C92" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D92" s="1" t="s">
@@ -3764,10 +3780,10 @@
       <c r="A93" t="s">
         <v>191</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="B93" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C93" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D93" s="1" t="s">
@@ -3784,10 +3800,10 @@
       <c r="A94" t="s">
         <v>193</v>
       </c>
-      <c r="B94" s="2" t="s">
+      <c r="B94" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C94" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D94" s="1" t="s">
@@ -3804,10 +3820,10 @@
       <c r="A95" t="s">
         <v>195</v>
       </c>
-      <c r="B95" s="2" t="s">
+      <c r="B95" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C95" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D95" s="1" t="s">
@@ -3824,10 +3840,10 @@
       <c r="A96" t="s">
         <v>197</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="B96" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="C96" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D96" s="1" t="s">
@@ -3844,10 +3860,10 @@
       <c r="A97" t="s">
         <v>199</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="B97" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="C97" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D97" s="1" t="s">
@@ -3864,10 +3880,10 @@
       <c r="A98" t="s">
         <v>201</v>
       </c>
-      <c r="B98" s="2" t="s">
+      <c r="B98" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="C98" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D98" s="1" t="s">
@@ -3884,10 +3900,10 @@
       <c r="A99" t="s">
         <v>203</v>
       </c>
-      <c r="B99" s="2" t="s">
+      <c r="B99" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="C99" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D99" s="1" t="s">
@@ -3904,10 +3920,10 @@
       <c r="A100" t="s">
         <v>205</v>
       </c>
-      <c r="B100" s="2" t="s">
+      <c r="B100" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="C100" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D100" s="1" t="s">
@@ -3924,10 +3940,10 @@
       <c r="A101" t="s">
         <v>207</v>
       </c>
-      <c r="B101" s="2" t="s">
+      <c r="B101" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="C101" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D101" s="1" t="s">
@@ -3944,10 +3960,10 @@
       <c r="A102" t="s">
         <v>209</v>
       </c>
-      <c r="B102" s="2" t="s">
+      <c r="B102" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="C102" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D102" s="1" t="s">
@@ -3964,10 +3980,10 @@
       <c r="A103" t="s">
         <v>211</v>
       </c>
-      <c r="B103" s="2" t="s">
+      <c r="B103" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="C103" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D103" s="1" t="s">
@@ -3984,10 +4000,10 @@
       <c r="A104" t="s">
         <v>213</v>
       </c>
-      <c r="B104" s="2" t="s">
+      <c r="B104" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="C104" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D104" s="1" t="s">
@@ -4004,10 +4020,10 @@
       <c r="A105" t="s">
         <v>215</v>
       </c>
-      <c r="B105" s="2" t="s">
+      <c r="B105" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="C105" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D105" s="1" t="s">
@@ -4024,10 +4040,10 @@
       <c r="A106" t="s">
         <v>217</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="B106" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="C106" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D106" s="1" t="s">
@@ -4044,10 +4060,10 @@
       <c r="A107" t="s">
         <v>219</v>
       </c>
-      <c r="B107" s="2" t="s">
+      <c r="B107" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="C107" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D107" s="1" t="s">
@@ -4064,10 +4080,10 @@
       <c r="A108" t="s">
         <v>221</v>
       </c>
-      <c r="B108" s="2" t="s">
+      <c r="B108" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="C108" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D108" s="1" t="s">
@@ -4084,10 +4100,10 @@
       <c r="A109" t="s">
         <v>223</v>
       </c>
-      <c r="B109" s="2" t="s">
+      <c r="B109" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="C109" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D109" s="1" t="s">
@@ -4104,10 +4120,10 @@
       <c r="A110" t="s">
         <v>225</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="B110" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="C110" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D110" s="1" t="s">
@@ -4124,10 +4140,10 @@
       <c r="A111" t="s">
         <v>227</v>
       </c>
-      <c r="B111" s="2" t="s">
+      <c r="B111" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="C111" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D111" s="1" t="s">
@@ -4144,10 +4160,10 @@
       <c r="A112" t="s">
         <v>229</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="B112" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="C112" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D112" s="1" t="s">
@@ -4164,10 +4180,10 @@
       <c r="A113" t="s">
         <v>231</v>
       </c>
-      <c r="B113" s="2" t="s">
+      <c r="B113" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="C113" s="1" t="s">
+      <c r="C113" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D113" s="1" t="s">
@@ -4184,10 +4200,10 @@
       <c r="A114" t="s">
         <v>233</v>
       </c>
-      <c r="B114" s="2" t="s">
+      <c r="B114" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="C114" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D114" s="1" t="s">
@@ -4204,10 +4220,10 @@
       <c r="A115" t="s">
         <v>235</v>
       </c>
-      <c r="B115" s="2" t="s">
+      <c r="B115" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="C115" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D115" s="1" t="s">
@@ -4224,10 +4240,10 @@
       <c r="A116" t="s">
         <v>237</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="B116" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="C116" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D116" s="1" t="s">
@@ -4244,10 +4260,10 @@
       <c r="A117" t="s">
         <v>239</v>
       </c>
-      <c r="B117" s="2" t="s">
+      <c r="B117" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="C117" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D117" s="1" t="s">
@@ -4264,10 +4280,10 @@
       <c r="A118" t="s">
         <v>241</v>
       </c>
-      <c r="B118" s="2" t="s">
+      <c r="B118" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="C118" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D118" s="1" t="s">
@@ -4284,10 +4300,10 @@
       <c r="A119" t="s">
         <v>243</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="B119" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="C119" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D119" s="1" t="s">
@@ -4304,10 +4320,10 @@
       <c r="A120" t="s">
         <v>245</v>
       </c>
-      <c r="B120" s="2" t="s">
+      <c r="B120" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="C120" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D120" s="1" t="s">
@@ -4324,10 +4340,10 @@
       <c r="A121" t="s">
         <v>247</v>
       </c>
-      <c r="B121" s="2" t="s">
+      <c r="B121" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="C121" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D121" s="1" t="s">
@@ -4344,10 +4360,10 @@
       <c r="A122" t="s">
         <v>249</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="B122" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="C122" s="1" t="s">
+      <c r="C122" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D122" s="1" t="s">
@@ -4364,10 +4380,10 @@
       <c r="A123" t="s">
         <v>251</v>
       </c>
-      <c r="B123" s="2" t="s">
+      <c r="B123" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="C123" s="1" t="s">
+      <c r="C123" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D123" s="1" t="s">
@@ -4384,10 +4400,10 @@
       <c r="A124" t="s">
         <v>253</v>
       </c>
-      <c r="B124" s="2" t="s">
+      <c r="B124" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="C124" s="1" t="s">
+      <c r="C124" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D124" s="1" t="s">
@@ -4404,10 +4420,10 @@
       <c r="A125" t="s">
         <v>255</v>
       </c>
-      <c r="B125" s="2" t="s">
+      <c r="B125" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="C125" s="1" t="s">
+      <c r="C125" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D125" s="1" t="s">
@@ -4424,10 +4440,10 @@
       <c r="A126" t="s">
         <v>257</v>
       </c>
-      <c r="B126" s="2" t="s">
+      <c r="B126" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="C126" s="1" t="s">
+      <c r="C126" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D126" s="1" t="s">
@@ -4444,10 +4460,10 @@
       <c r="A127" t="s">
         <v>259</v>
       </c>
-      <c r="B127" s="2" t="s">
+      <c r="B127" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="C127" s="1" t="s">
+      <c r="C127" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D127" s="1" t="s">
@@ -4464,10 +4480,10 @@
       <c r="A128" t="s">
         <v>261</v>
       </c>
-      <c r="B128" s="2" t="s">
+      <c r="B128" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="C128" s="1" t="s">
+      <c r="C128" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D128" s="1" t="s">
@@ -4484,10 +4500,10 @@
       <c r="A129" t="s">
         <v>263</v>
       </c>
-      <c r="B129" s="2" t="s">
+      <c r="B129" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="C129" s="1" t="s">
+      <c r="C129" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D129" s="1" t="s">
@@ -4504,10 +4520,10 @@
       <c r="A130" t="s">
         <v>265</v>
       </c>
-      <c r="B130" s="2" t="s">
+      <c r="B130" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="C130" s="1" t="s">
+      <c r="C130" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D130" s="1" t="s">
@@ -4524,10 +4540,10 @@
       <c r="A131" t="s">
         <v>267</v>
       </c>
-      <c r="B131" s="2" t="s">
+      <c r="B131" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="C131" s="1" t="s">
+      <c r="C131" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D131" s="1" t="s">
@@ -4544,10 +4560,10 @@
       <c r="A132" t="s">
         <v>269</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="B132" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="C132" s="1" t="s">
+      <c r="C132" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D132" s="1" t="s">
@@ -4564,10 +4580,10 @@
       <c r="A133" t="s">
         <v>271</v>
       </c>
-      <c r="B133" s="2" t="s">
+      <c r="B133" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="C133" s="1" t="s">
+      <c r="C133" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D133" s="1" t="s">
@@ -4584,10 +4600,10 @@
       <c r="A134" t="s">
         <v>273</v>
       </c>
-      <c r="B134" s="2" t="s">
+      <c r="B134" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="C134" s="1" t="s">
+      <c r="C134" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D134" s="1" t="s">
@@ -4604,10 +4620,10 @@
       <c r="A135" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B135" s="2" t="s">
+      <c r="B135" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="C135" s="1" t="s">
+      <c r="C135" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D135" s="1" t="s">
@@ -4624,10 +4640,10 @@
       <c r="A136" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B136" s="2" t="s">
+      <c r="B136" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="C136" s="1" t="s">
+      <c r="C136" s="4" t="s">
         <v>279</v>
       </c>
       <c r="D136" s="1" t="s">
@@ -4644,10 +4660,10 @@
       <c r="A137" t="s">
         <v>280</v>
       </c>
-      <c r="B137" s="2" t="s">
+      <c r="B137" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="C137" s="1" t="s">
+      <c r="C137" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D137" s="1" t="s">
@@ -4664,11 +4680,11 @@
       <c r="A138" t="s">
         <v>282</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="B138" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="C138" s="1">
-        <v>3</v>
+      <c r="C138" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>9</v>
@@ -4684,11 +4700,11 @@
       <c r="A139" t="s">
         <v>284</v>
       </c>
-      <c r="B139" s="2" t="s">
+      <c r="B139" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="C139" s="1">
-        <v>3</v>
+      <c r="C139" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>9</v>
@@ -4704,11 +4720,11 @@
       <c r="A140" t="s">
         <v>286</v>
       </c>
-      <c r="B140" s="2" t="s">
+      <c r="B140" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="C140" s="1">
-        <v>3</v>
+      <c r="C140" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>9</v>
@@ -4724,11 +4740,11 @@
       <c r="A141" t="s">
         <v>288</v>
       </c>
-      <c r="B141" s="2" t="s">
+      <c r="B141" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="C141" s="1">
-        <v>3</v>
+      <c r="C141" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>9</v>
@@ -4744,11 +4760,11 @@
       <c r="A142" t="s">
         <v>290</v>
       </c>
-      <c r="B142" s="2" t="s">
+      <c r="B142" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="C142" s="1">
-        <v>3</v>
+      <c r="C142" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>9</v>
@@ -4764,11 +4780,11 @@
       <c r="A143" t="s">
         <v>292</v>
       </c>
-      <c r="B143" s="2" t="s">
+      <c r="B143" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="C143" s="1">
-        <v>3</v>
+      <c r="C143" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>9</v>
@@ -4784,11 +4800,11 @@
       <c r="A144" t="s">
         <v>294</v>
       </c>
-      <c r="B144" s="2" t="s">
+      <c r="B144" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="C144" s="1">
-        <v>3</v>
+      <c r="C144" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>9</v>
@@ -4804,11 +4820,11 @@
       <c r="A145" t="s">
         <v>296</v>
       </c>
-      <c r="B145" s="2" t="s">
+      <c r="B145" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="C145" s="1">
-        <v>3</v>
+      <c r="C145" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>9</v>
@@ -4824,11 +4840,11 @@
       <c r="A146" t="s">
         <v>298</v>
       </c>
-      <c r="B146" s="2" t="s">
+      <c r="B146" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="C146" s="1">
-        <v>3</v>
+      <c r="C146" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>9</v>
@@ -4844,11 +4860,11 @@
       <c r="A147" t="s">
         <v>300</v>
       </c>
-      <c r="B147" s="2" t="s">
+      <c r="B147" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="C147" s="1">
-        <v>3</v>
+      <c r="C147" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>9</v>
@@ -4864,11 +4880,11 @@
       <c r="A148" t="s">
         <v>302</v>
       </c>
-      <c r="B148" s="2" t="s">
+      <c r="B148" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="C148" s="1">
-        <v>3</v>
+      <c r="C148" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>9</v>
@@ -4884,11 +4900,11 @@
       <c r="A149" t="s">
         <v>304</v>
       </c>
-      <c r="B149" s="2" t="s">
+      <c r="B149" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="C149" s="1">
-        <v>3</v>
+      <c r="C149" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>9</v>
@@ -4904,11 +4920,11 @@
       <c r="A150" t="s">
         <v>306</v>
       </c>
-      <c r="B150" s="2" t="s">
+      <c r="B150" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="C150" s="1">
-        <v>3</v>
+      <c r="C150" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>9</v>
@@ -4924,23 +4940,46 @@
       <c r="A151" t="s">
         <v>308</v>
       </c>
-      <c r="B151" s="2" t="s">
+      <c r="B151" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="C151" s="1">
+      <c r="C151" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E151" t="s">
+        <v>10</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="A152" t="s">
+        <v>310</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C152" s="4">
         <v>3</v>
       </c>
-      <c r="D151" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E151" t="s">
-        <v>10</v>
-      </c>
-      <c r="F151" s="1" t="s">
+      <c r="D152" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E152" t="s">
+        <v>10</v>
+      </c>
+      <c r="F152" s="1" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F151" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <conditionalFormatting sqref="B$1:B$1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>

--- a/testdata/listForExecution.xlsx
+++ b/testdata/listForExecution.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$151</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$153</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="911" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="316">
   <si>
     <t>TestName</t>
   </si>
@@ -966,6 +966,18 @@
   </si>
   <si>
     <t>C70915</t>
+  </si>
+  <si>
+    <t>Payments_Own_Account_Transfer_From_Current_Foreign_Account_To_Current_Foreign_Account_[WEB]</t>
+  </si>
+  <si>
+    <t>C70916</t>
+  </si>
+  <si>
+    <t>Payments_Own_Account_Transfer_To_Loan_[WEB]</t>
+  </si>
+  <si>
+    <t>C70917</t>
   </si>
 </sst>
 </file>
@@ -1928,7 +1940,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F152"/>
+  <dimension ref="A1:F154"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="94.1428571428571" customWidth="1"/>
@@ -4976,8 +4988,48 @@
         <v>11</v>
       </c>
     </row>
+    <row r="153" spans="1:6">
+      <c r="A153" t="s">
+        <v>312</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C153" s="4">
+        <v>3</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E153" t="s">
+        <v>10</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="A154" t="s">
+        <v>314</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C154" s="4">
+        <v>3</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E154" t="s">
+        <v>10</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F151" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F153" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="B$1:B$1048576">

--- a/testdata/listForExecution.xlsx
+++ b/testdata/listForExecution.xlsx
@@ -4,14 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8340"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$153</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -30,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="323">
   <si>
     <t>TestName</t>
   </si>
@@ -878,106 +875,127 @@
     <t>C70900</t>
   </si>
   <si>
+    <t>Payments_Currency_Exchange_Pricelist_[WEB]-Overview</t>
+  </si>
+  <si>
+    <t>C70901</t>
+  </si>
+  <si>
+    <t>Saving_Accounts_Transactions_Download_Option_[WEB]</t>
+  </si>
+  <si>
+    <t>C70902</t>
+  </si>
+  <si>
+    <t>Payments_Own_Account_Transfer_To_Loan_[WEB]</t>
+  </si>
+  <si>
+    <t>C70903</t>
+  </si>
+  <si>
+    <t>Payments_Own_Account_Transfer_From_Current_Foreign_Account_To_Current_Foreign_Account_[WEB]</t>
+  </si>
+  <si>
+    <t>C70904</t>
+  </si>
+  <si>
+    <t>Payments_Currency_Exchange_[WEB]-Buy_From_Payment</t>
+  </si>
+  <si>
+    <t>C70905</t>
+  </si>
+  <si>
+    <t>Payments_Currency_Exchange_[WEB]-Sell_From_Payment</t>
+  </si>
+  <si>
+    <t>C70906</t>
+  </si>
+  <si>
+    <t>Savings_Accounts_Transactions_Filter_By_Date_Date_Picker_[WEB]</t>
+  </si>
+  <si>
+    <t>C70907</t>
+  </si>
+  <si>
+    <t>Payments_Recipient_Template_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70908</t>
+  </si>
+  <si>
+    <t>Payments_Upcoming_Payments_Details_Of_Payments_Transaction_On_The_List_Of_Transaction_[WEB]</t>
+  </si>
+  <si>
+    <t>C70909</t>
+  </si>
+  <si>
+    <t>C70910</t>
+  </si>
+  <si>
+    <t>Payments_Payments_Archive_Payments_Details_[WEB]</t>
+  </si>
+  <si>
+    <t>C70911</t>
+  </si>
+  <si>
+    <t>Current_Accounts_RSD_Statemants_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70912</t>
+  </si>
+  <si>
+    <t>Current_Foreign_Accounts_Statemants_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70913</t>
+  </si>
+  <si>
+    <t>Saving_Accounts_Accounts_Statemants_List_[WEB]</t>
+  </si>
+  <si>
+    <t>C70914</t>
+  </si>
+  <si>
     <t>Payments_Domestic_Payments_Internal_Urgent_Payment_[WEB]</t>
   </si>
   <si>
-    <t>C70901</t>
-  </si>
-  <si>
     <t>Payments_Domestic_Payments_Internal_Non_Urgent_Payment_[WEB]</t>
   </si>
   <si>
-    <t>C70902</t>
-  </si>
-  <si>
     <t>Payments_Domestic_Payments_External_Urgent_Payment_No_Model_[WEB]</t>
   </si>
   <si>
-    <t>C70903</t>
-  </si>
-  <si>
     <t>Payments_Domestic_Payments_External_Urgent_Payment_Model11_Invalid_Bez_Poziva_Na_Broj_[WEB]</t>
   </si>
   <si>
-    <t>C70904</t>
-  </si>
-  <si>
     <t>Payments_Domestic_Payments_External_Non_Urgent_Payment_Model11_[WEB]</t>
   </si>
   <si>
-    <t>C70905</t>
-  </si>
-  <si>
     <t>Payments_Domestic_Payments_External_Urgent_Payment_Model97_Invalid_Bez_Poziva_Na_Broj_[WEB]</t>
   </si>
   <si>
-    <t>C70906</t>
-  </si>
-  <si>
     <t>Payments_Domestic_Payments_External_Non_Urgent_Payment_Model97_[WEB]</t>
   </si>
   <si>
-    <t>C70907</t>
-  </si>
-  <si>
     <t>Payments_Domestic_Payments_Budzetski_Urgent_Payment_Purpose_Code_289_Invalid_[WEB]</t>
   </si>
   <si>
-    <t>C70908</t>
-  </si>
-  <si>
     <t>Payments_Domestic_Payments_Budzetski_Urgent_Payment_Without_Reference_Number_Invalid_[WEB]</t>
   </si>
   <si>
-    <t>C70909</t>
-  </si>
-  <si>
     <t>Payments_Domestic_Payments_Budzetski_Urgent_Payment_Model97_[WEB]</t>
   </si>
   <si>
-    <t>C70910</t>
-  </si>
-  <si>
     <t>Payments_Domestic_Payments_Budzetski_Non_Urgent_Payment_Model97_[WEB]</t>
   </si>
   <si>
-    <t>C70911</t>
-  </si>
-  <si>
     <t>Payments_Domestic_Payments_External_Urgent_Payment_Model97_[WEB]</t>
   </si>
   <si>
-    <t>C70912</t>
-  </si>
-  <si>
     <t>Payments_Domestic_Payments_External_Urgent_Payment_Model11_[WEB]</t>
   </si>
   <si>
-    <t>C70913</t>
-  </si>
-  <si>
     <t>Payments_Domestic_Payments_External_Non_Urgent_Payment_No_Model_[WEB]</t>
-  </si>
-  <si>
-    <t>C70914</t>
-  </si>
-  <si>
-    <t>Payments_Recipient_Last_5_Payments_Of_Recipient_[WEB]-View_And_Repeat</t>
-  </si>
-  <si>
-    <t>C70915</t>
-  </si>
-  <si>
-    <t>Payments_Own_Account_Transfer_From_Current_Foreign_Account_To_Current_Foreign_Account_[WEB]</t>
-  </si>
-  <si>
-    <t>C70916</t>
-  </si>
-  <si>
-    <t>Payments_Own_Account_Transfer_To_Loan_[WEB]</t>
-  </si>
-  <si>
-    <t>C70917</t>
   </si>
 </sst>
 </file>
@@ -1597,13 +1615,10 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1940,12 +1955,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F154"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="5"/>
+  <dimension ref="A1:F165"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="94.1428571428571" customWidth="1"/>
-    <col min="2" max="2" width="11.7142857142857" customWidth="1"/>
-    <col min="3" max="3" width="9" style="2"/>
+    <col min="1" max="1" width="91.1388888888889" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1955,7 +1968,7 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -1972,10 +1985,10 @@
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -1992,10 +2005,10 @@
       <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -2012,10 +2025,10 @@
       <c r="A4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -2032,10 +2045,10 @@
       <c r="A5" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -2052,10 +2065,10 @@
       <c r="A6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -2072,10 +2085,10 @@
       <c r="A7" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -2092,10 +2105,10 @@
       <c r="A8" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -2112,10 +2125,10 @@
       <c r="A9" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -2132,10 +2145,10 @@
       <c r="A10" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -2152,10 +2165,10 @@
       <c r="A11" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -2172,10 +2185,10 @@
       <c r="A12" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -2192,10 +2205,10 @@
       <c r="A13" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
@@ -2212,10 +2225,10 @@
       <c r="A14" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -2232,10 +2245,10 @@
       <c r="A15" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="1" t="s">
@@ -2252,10 +2265,10 @@
       <c r="A16" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -2272,10 +2285,10 @@
       <c r="A17" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="1" t="s">
@@ -2292,10 +2305,10 @@
       <c r="A18" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D18" s="1" t="s">
@@ -2312,10 +2325,10 @@
       <c r="A19" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D19" s="1" t="s">
@@ -2332,10 +2345,10 @@
       <c r="A20" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D20" s="1" t="s">
@@ -2352,10 +2365,10 @@
       <c r="A21" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D21" s="1" t="s">
@@ -2372,10 +2385,10 @@
       <c r="A22" t="s">
         <v>50</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D22" s="1" t="s">
@@ -2392,10 +2405,10 @@
       <c r="A23" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D23" s="1" t="s">
@@ -2412,10 +2425,10 @@
       <c r="A24" t="s">
         <v>54</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="1" t="s">
@@ -2432,10 +2445,10 @@
       <c r="A25" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="1" t="s">
@@ -2452,10 +2465,10 @@
       <c r="A26" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D26" s="1" t="s">
@@ -2472,10 +2485,10 @@
       <c r="A27" t="s">
         <v>60</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="1" t="s">
@@ -2492,10 +2505,10 @@
       <c r="A28" t="s">
         <v>62</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="1" t="s">
@@ -2512,10 +2525,10 @@
       <c r="A29" t="s">
         <v>64</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D29" s="1" t="s">
@@ -2532,10 +2545,10 @@
       <c r="A30" t="s">
         <v>66</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D30" s="1" t="s">
@@ -2552,10 +2565,10 @@
       <c r="A31" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D31" s="1" t="s">
@@ -2572,10 +2585,10 @@
       <c r="A32" t="s">
         <v>70</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D32" s="1" t="s">
@@ -2592,10 +2605,10 @@
       <c r="A33" t="s">
         <v>72</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D33" s="1" t="s">
@@ -2612,10 +2625,10 @@
       <c r="A34" t="s">
         <v>74</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D34" s="1" t="s">
@@ -2632,10 +2645,10 @@
       <c r="A35" t="s">
         <v>76</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D35" s="1" t="s">
@@ -2652,10 +2665,10 @@
       <c r="A36" t="s">
         <v>78</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D36" s="1" t="s">
@@ -2672,10 +2685,10 @@
       <c r="A37" t="s">
         <v>80</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D37" s="1" t="s">
@@ -2692,10 +2705,10 @@
       <c r="A38" t="s">
         <v>82</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D38" s="1" t="s">
@@ -2712,10 +2725,10 @@
       <c r="A39" t="s">
         <v>84</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D39" s="1" t="s">
@@ -2732,10 +2745,10 @@
       <c r="A40" t="s">
         <v>86</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D40" s="1" t="s">
@@ -2752,10 +2765,10 @@
       <c r="A41" t="s">
         <v>88</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D41" s="1" t="s">
@@ -2772,10 +2785,10 @@
       <c r="A42" t="s">
         <v>90</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D42" s="1" t="s">
@@ -2792,10 +2805,10 @@
       <c r="A43" t="s">
         <v>92</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D43" s="1" t="s">
@@ -2812,10 +2825,10 @@
       <c r="A44" t="s">
         <v>94</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="1" t="s">
@@ -2832,10 +2845,10 @@
       <c r="A45" t="s">
         <v>96</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D45" s="1" t="s">
@@ -2852,10 +2865,10 @@
       <c r="A46" t="s">
         <v>98</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D46" s="1" t="s">
@@ -2872,10 +2885,10 @@
       <c r="A47" t="s">
         <v>100</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D47" s="1" t="s">
@@ -2892,10 +2905,10 @@
       <c r="A48" t="s">
         <v>102</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D48" s="1" t="s">
@@ -2912,10 +2925,10 @@
       <c r="A49" t="s">
         <v>104</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="C49" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D49" s="1" t="s">
@@ -2932,10 +2945,10 @@
       <c r="A50" t="s">
         <v>106</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D50" s="1" t="s">
@@ -2952,10 +2965,10 @@
       <c r="A51" t="s">
         <v>108</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B51" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C51" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D51" s="1" t="s">
@@ -2972,10 +2985,10 @@
       <c r="A52" t="s">
         <v>110</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D52" s="1" t="s">
@@ -2992,10 +3005,10 @@
       <c r="A53" t="s">
         <v>112</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B53" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C53" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D53" s="1" t="s">
@@ -3012,10 +3025,10 @@
       <c r="A54" t="s">
         <v>114</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D54" s="1" t="s">
@@ -3032,10 +3045,10 @@
       <c r="A55" t="s">
         <v>116</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B55" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="C55" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D55" s="1" t="s">
@@ -3052,10 +3065,10 @@
       <c r="A56" t="s">
         <v>118</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C56" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D56" s="1" t="s">
@@ -3072,10 +3085,10 @@
       <c r="A57" t="s">
         <v>120</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B57" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C57" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D57" s="1" t="s">
@@ -3092,10 +3105,10 @@
       <c r="A58" t="s">
         <v>122</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B58" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C58" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D58" s="1" t="s">
@@ -3112,10 +3125,10 @@
       <c r="A59" t="s">
         <v>124</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B59" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="C59" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D59" s="1" t="s">
@@ -3132,10 +3145,10 @@
       <c r="A60" t="s">
         <v>126</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B60" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C60" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D60" s="1" t="s">
@@ -3152,10 +3165,10 @@
       <c r="A61" t="s">
         <v>128</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B61" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C61" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D61" s="1" t="s">
@@ -3172,10 +3185,10 @@
       <c r="A62" t="s">
         <v>130</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="C62" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D62" s="1" t="s">
@@ -3192,10 +3205,10 @@
       <c r="A63" t="s">
         <v>132</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B63" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="C63" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D63" s="1" t="s">
@@ -3212,10 +3225,10 @@
       <c r="A64" t="s">
         <v>134</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B64" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="C64" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D64" s="1" t="s">
@@ -3232,10 +3245,10 @@
       <c r="A65" t="s">
         <v>136</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="C65" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D65" s="1" t="s">
@@ -3252,10 +3265,10 @@
       <c r="A66" t="s">
         <v>138</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B66" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="C66" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D66" s="1" t="s">
@@ -3272,10 +3285,10 @@
       <c r="A67" t="s">
         <v>140</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B67" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C67" s="4" t="s">
+      <c r="C67" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D67" s="1" t="s">
@@ -3292,10 +3305,10 @@
       <c r="A68" t="s">
         <v>142</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B68" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="C68" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D68" s="1" t="s">
@@ -3312,10 +3325,10 @@
       <c r="A69" t="s">
         <v>144</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B69" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="C69" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D69" s="1" t="s">
@@ -3332,10 +3345,10 @@
       <c r="A70" t="s">
         <v>146</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B70" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="C70" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D70" s="1" t="s">
@@ -3352,10 +3365,10 @@
       <c r="A71" t="s">
         <v>148</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B71" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="C71" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D71" s="1" t="s">
@@ -3372,10 +3385,10 @@
       <c r="A72" t="s">
         <v>150</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="B72" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C72" s="4" t="s">
+      <c r="C72" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D72" s="1" t="s">
@@ -3392,10 +3405,10 @@
       <c r="A73" t="s">
         <v>152</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B73" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C73" s="4" t="s">
+      <c r="C73" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D73" s="1" t="s">
@@ -3412,10 +3425,10 @@
       <c r="A74" t="s">
         <v>154</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B74" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D74" s="1" t="s">
@@ -3432,10 +3445,10 @@
       <c r="A75" t="s">
         <v>156</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B75" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C75" s="4" t="s">
+      <c r="C75" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D75" s="1" t="s">
@@ -3452,10 +3465,10 @@
       <c r="A76" t="s">
         <v>158</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B76" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C76" s="4" t="s">
+      <c r="C76" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D76" s="1" t="s">
@@ -3472,10 +3485,10 @@
       <c r="A77" t="s">
         <v>160</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B77" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C77" s="4" t="s">
+      <c r="C77" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D77" s="1" t="s">
@@ -3492,10 +3505,10 @@
       <c r="A78" t="s">
         <v>162</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="B78" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C78" s="4" t="s">
+      <c r="C78" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D78" s="1" t="s">
@@ -3512,10 +3525,10 @@
       <c r="A79" t="s">
         <v>164</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B79" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C79" s="4" t="s">
+      <c r="C79" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D79" s="1" t="s">
@@ -3532,10 +3545,10 @@
       <c r="A80" t="s">
         <v>166</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="B80" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C80" s="4" t="s">
+      <c r="C80" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D80" s="1" t="s">
@@ -3552,10 +3565,10 @@
       <c r="A81" t="s">
         <v>168</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="B81" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="C81" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D81" s="1" t="s">
@@ -3572,10 +3585,10 @@
       <c r="A82" t="s">
         <v>170</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="B82" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C82" s="4" t="s">
+      <c r="C82" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D82" s="1" t="s">
@@ -3592,10 +3605,10 @@
       <c r="A83" t="s">
         <v>172</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="B83" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="C83" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D83" s="1" t="s">
@@ -3612,10 +3625,10 @@
       <c r="A84" t="s">
         <v>174</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="B84" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C84" s="4" t="s">
+      <c r="C84" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D84" s="1" t="s">
@@ -3632,10 +3645,10 @@
       <c r="A85" t="s">
         <v>176</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="B85" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C85" s="4" t="s">
+      <c r="C85" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D85" s="1" t="s">
@@ -3652,10 +3665,10 @@
       <c r="A86" t="s">
         <v>178</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="B86" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C86" s="4" t="s">
+      <c r="C86" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D86" s="1" t="s">
@@ -3672,10 +3685,10 @@
       <c r="A87" t="s">
         <v>166</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="B87" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C87" s="4" t="s">
+      <c r="C87" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D87" s="1" t="s">
@@ -3692,10 +3705,10 @@
       <c r="A88" t="s">
         <v>181</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="B88" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C88" s="4" t="s">
+      <c r="C88" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D88" s="1" t="s">
@@ -3712,10 +3725,10 @@
       <c r="A89" t="s">
         <v>183</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="B89" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="C89" s="4" t="s">
+      <c r="C89" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D89" s="1" t="s">
@@ -3732,10 +3745,10 @@
       <c r="A90" t="s">
         <v>185</v>
       </c>
-      <c r="B90" s="3" t="s">
+      <c r="B90" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C90" s="4" t="s">
+      <c r="C90" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D90" s="1" t="s">
@@ -3752,10 +3765,10 @@
       <c r="A91" t="s">
         <v>187</v>
       </c>
-      <c r="B91" s="3" t="s">
+      <c r="B91" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C91" s="4" t="s">
+      <c r="C91" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D91" s="1" t="s">
@@ -3772,10 +3785,10 @@
       <c r="A92" t="s">
         <v>189</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="B92" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C92" s="4" t="s">
+      <c r="C92" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D92" s="1" t="s">
@@ -3792,10 +3805,10 @@
       <c r="A93" t="s">
         <v>191</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="B93" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C93" s="4" t="s">
+      <c r="C93" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D93" s="1" t="s">
@@ -3812,10 +3825,10 @@
       <c r="A94" t="s">
         <v>193</v>
       </c>
-      <c r="B94" s="3" t="s">
+      <c r="B94" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C94" s="4" t="s">
+      <c r="C94" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D94" s="1" t="s">
@@ -3832,10 +3845,10 @@
       <c r="A95" t="s">
         <v>195</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="B95" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="C95" s="4" t="s">
+      <c r="C95" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D95" s="1" t="s">
@@ -3852,10 +3865,10 @@
       <c r="A96" t="s">
         <v>197</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="B96" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C96" s="4" t="s">
+      <c r="C96" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D96" s="1" t="s">
@@ -3872,10 +3885,10 @@
       <c r="A97" t="s">
         <v>199</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="B97" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C97" s="4" t="s">
+      <c r="C97" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D97" s="1" t="s">
@@ -3892,10 +3905,10 @@
       <c r="A98" t="s">
         <v>201</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="B98" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="C98" s="4" t="s">
+      <c r="C98" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D98" s="1" t="s">
@@ -3912,10 +3925,10 @@
       <c r="A99" t="s">
         <v>203</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="B99" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C99" s="4" t="s">
+      <c r="C99" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D99" s="1" t="s">
@@ -3932,10 +3945,10 @@
       <c r="A100" t="s">
         <v>205</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="B100" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="C100" s="4" t="s">
+      <c r="C100" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D100" s="1" t="s">
@@ -3952,10 +3965,10 @@
       <c r="A101" t="s">
         <v>207</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="B101" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="C101" s="4" t="s">
+      <c r="C101" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D101" s="1" t="s">
@@ -3972,10 +3985,10 @@
       <c r="A102" t="s">
         <v>209</v>
       </c>
-      <c r="B102" s="3" t="s">
+      <c r="B102" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C102" s="4" t="s">
+      <c r="C102" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D102" s="1" t="s">
@@ -3992,10 +4005,10 @@
       <c r="A103" t="s">
         <v>211</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="B103" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="C103" s="4" t="s">
+      <c r="C103" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D103" s="1" t="s">
@@ -4012,10 +4025,10 @@
       <c r="A104" t="s">
         <v>213</v>
       </c>
-      <c r="B104" s="3" t="s">
+      <c r="B104" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="C104" s="4" t="s">
+      <c r="C104" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D104" s="1" t="s">
@@ -4032,10 +4045,10 @@
       <c r="A105" t="s">
         <v>215</v>
       </c>
-      <c r="B105" s="3" t="s">
+      <c r="B105" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C105" s="4" t="s">
+      <c r="C105" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D105" s="1" t="s">
@@ -4052,10 +4065,10 @@
       <c r="A106" t="s">
         <v>217</v>
       </c>
-      <c r="B106" s="3" t="s">
+      <c r="B106" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="C106" s="4" t="s">
+      <c r="C106" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D106" s="1" t="s">
@@ -4072,10 +4085,10 @@
       <c r="A107" t="s">
         <v>219</v>
       </c>
-      <c r="B107" s="3" t="s">
+      <c r="B107" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="C107" s="4" t="s">
+      <c r="C107" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D107" s="1" t="s">
@@ -4092,10 +4105,10 @@
       <c r="A108" t="s">
         <v>221</v>
       </c>
-      <c r="B108" s="3" t="s">
+      <c r="B108" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C108" s="4" t="s">
+      <c r="C108" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D108" s="1" t="s">
@@ -4112,10 +4125,10 @@
       <c r="A109" t="s">
         <v>223</v>
       </c>
-      <c r="B109" s="3" t="s">
+      <c r="B109" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="C109" s="4" t="s">
+      <c r="C109" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D109" s="1" t="s">
@@ -4132,10 +4145,10 @@
       <c r="A110" t="s">
         <v>225</v>
       </c>
-      <c r="B110" s="3" t="s">
+      <c r="B110" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="C110" s="4" t="s">
+      <c r="C110" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D110" s="1" t="s">
@@ -4152,10 +4165,10 @@
       <c r="A111" t="s">
         <v>227</v>
       </c>
-      <c r="B111" s="3" t="s">
+      <c r="B111" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C111" s="4" t="s">
+      <c r="C111" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D111" s="1" t="s">
@@ -4172,10 +4185,10 @@
       <c r="A112" t="s">
         <v>229</v>
       </c>
-      <c r="B112" s="3" t="s">
+      <c r="B112" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="C112" s="4" t="s">
+      <c r="C112" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D112" s="1" t="s">
@@ -4192,10 +4205,10 @@
       <c r="A113" t="s">
         <v>231</v>
       </c>
-      <c r="B113" s="3" t="s">
+      <c r="B113" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="C113" s="4" t="s">
+      <c r="C113" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D113" s="1" t="s">
@@ -4212,10 +4225,10 @@
       <c r="A114" t="s">
         <v>233</v>
       </c>
-      <c r="B114" s="3" t="s">
+      <c r="B114" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="C114" s="4" t="s">
+      <c r="C114" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D114" s="1" t="s">
@@ -4232,10 +4245,10 @@
       <c r="A115" t="s">
         <v>235</v>
       </c>
-      <c r="B115" s="3" t="s">
+      <c r="B115" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="C115" s="4" t="s">
+      <c r="C115" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D115" s="1" t="s">
@@ -4252,10 +4265,10 @@
       <c r="A116" t="s">
         <v>237</v>
       </c>
-      <c r="B116" s="3" t="s">
+      <c r="B116" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="C116" s="4" t="s">
+      <c r="C116" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D116" s="1" t="s">
@@ -4272,10 +4285,10 @@
       <c r="A117" t="s">
         <v>239</v>
       </c>
-      <c r="B117" s="3" t="s">
+      <c r="B117" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="C117" s="4" t="s">
+      <c r="C117" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D117" s="1" t="s">
@@ -4292,10 +4305,10 @@
       <c r="A118" t="s">
         <v>241</v>
       </c>
-      <c r="B118" s="3" t="s">
+      <c r="B118" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="C118" s="4" t="s">
+      <c r="C118" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D118" s="1" t="s">
@@ -4312,10 +4325,10 @@
       <c r="A119" t="s">
         <v>243</v>
       </c>
-      <c r="B119" s="3" t="s">
+      <c r="B119" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="C119" s="4" t="s">
+      <c r="C119" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D119" s="1" t="s">
@@ -4332,10 +4345,10 @@
       <c r="A120" t="s">
         <v>245</v>
       </c>
-      <c r="B120" s="3" t="s">
+      <c r="B120" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C120" s="4" t="s">
+      <c r="C120" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D120" s="1" t="s">
@@ -4352,10 +4365,10 @@
       <c r="A121" t="s">
         <v>247</v>
       </c>
-      <c r="B121" s="3" t="s">
+      <c r="B121" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="C121" s="4" t="s">
+      <c r="C121" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D121" s="1" t="s">
@@ -4372,10 +4385,10 @@
       <c r="A122" t="s">
         <v>249</v>
       </c>
-      <c r="B122" s="3" t="s">
+      <c r="B122" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="C122" s="4" t="s">
+      <c r="C122" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D122" s="1" t="s">
@@ -4392,10 +4405,10 @@
       <c r="A123" t="s">
         <v>251</v>
       </c>
-      <c r="B123" s="3" t="s">
+      <c r="B123" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="C123" s="4" t="s">
+      <c r="C123" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D123" s="1" t="s">
@@ -4412,10 +4425,10 @@
       <c r="A124" t="s">
         <v>253</v>
       </c>
-      <c r="B124" s="3" t="s">
+      <c r="B124" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C124" s="4" t="s">
+      <c r="C124" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D124" s="1" t="s">
@@ -4432,10 +4445,10 @@
       <c r="A125" t="s">
         <v>255</v>
       </c>
-      <c r="B125" s="3" t="s">
+      <c r="B125" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="C125" s="4" t="s">
+      <c r="C125" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D125" s="1" t="s">
@@ -4452,10 +4465,10 @@
       <c r="A126" t="s">
         <v>257</v>
       </c>
-      <c r="B126" s="3" t="s">
+      <c r="B126" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="C126" s="4" t="s">
+      <c r="C126" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D126" s="1" t="s">
@@ -4472,10 +4485,10 @@
       <c r="A127" t="s">
         <v>259</v>
       </c>
-      <c r="B127" s="3" t="s">
+      <c r="B127" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="C127" s="4" t="s">
+      <c r="C127" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D127" s="1" t="s">
@@ -4492,10 +4505,10 @@
       <c r="A128" t="s">
         <v>261</v>
       </c>
-      <c r="B128" s="3" t="s">
+      <c r="B128" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="C128" s="4" t="s">
+      <c r="C128" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D128" s="1" t="s">
@@ -4512,10 +4525,10 @@
       <c r="A129" t="s">
         <v>263</v>
       </c>
-      <c r="B129" s="3" t="s">
+      <c r="B129" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="C129" s="4" t="s">
+      <c r="C129" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D129" s="1" t="s">
@@ -4532,10 +4545,10 @@
       <c r="A130" t="s">
         <v>265</v>
       </c>
-      <c r="B130" s="3" t="s">
+      <c r="B130" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="C130" s="4" t="s">
+      <c r="C130" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D130" s="1" t="s">
@@ -4552,10 +4565,10 @@
       <c r="A131" t="s">
         <v>267</v>
       </c>
-      <c r="B131" s="3" t="s">
+      <c r="B131" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C131" s="4" t="s">
+      <c r="C131" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D131" s="1" t="s">
@@ -4572,10 +4585,10 @@
       <c r="A132" t="s">
         <v>269</v>
       </c>
-      <c r="B132" s="3" t="s">
+      <c r="B132" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="C132" s="4" t="s">
+      <c r="C132" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D132" s="1" t="s">
@@ -4592,10 +4605,10 @@
       <c r="A133" t="s">
         <v>271</v>
       </c>
-      <c r="B133" s="3" t="s">
+      <c r="B133" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="C133" s="4" t="s">
+      <c r="C133" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D133" s="1" t="s">
@@ -4612,10 +4625,10 @@
       <c r="A134" t="s">
         <v>273</v>
       </c>
-      <c r="B134" s="3" t="s">
+      <c r="B134" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="C134" s="4" t="s">
+      <c r="C134" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D134" s="1" t="s">
@@ -4632,10 +4645,10 @@
       <c r="A135" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="B135" s="3" t="s">
+      <c r="B135" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="C135" s="4" t="s">
+      <c r="C135" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D135" s="1" t="s">
@@ -4652,10 +4665,10 @@
       <c r="A136" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B136" s="3" t="s">
+      <c r="B136" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="C136" s="4" t="s">
+      <c r="C136" s="1" t="s">
         <v>279</v>
       </c>
       <c r="D136" s="1" t="s">
@@ -4672,10 +4685,10 @@
       <c r="A137" t="s">
         <v>280</v>
       </c>
-      <c r="B137" s="3" t="s">
+      <c r="B137" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="C137" s="4" t="s">
+      <c r="C137" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D137" s="1" t="s">
@@ -4692,10 +4705,10 @@
       <c r="A138" t="s">
         <v>282</v>
       </c>
-      <c r="B138" s="3" t="s">
+      <c r="B138" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="C138" s="4" t="s">
+      <c r="C138" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D138" s="1" t="s">
@@ -4712,10 +4725,10 @@
       <c r="A139" t="s">
         <v>284</v>
       </c>
-      <c r="B139" s="3" t="s">
+      <c r="B139" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C139" s="4" t="s">
+      <c r="C139" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D139" s="1" t="s">
@@ -4732,10 +4745,10 @@
       <c r="A140" t="s">
         <v>286</v>
       </c>
-      <c r="B140" s="3" t="s">
+      <c r="B140" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="C140" s="4" t="s">
+      <c r="C140" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D140" s="1" t="s">
@@ -4752,10 +4765,10 @@
       <c r="A141" t="s">
         <v>288</v>
       </c>
-      <c r="B141" s="3" t="s">
+      <c r="B141" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C141" s="4" t="s">
+      <c r="C141" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D141" s="1" t="s">
@@ -4772,10 +4785,10 @@
       <c r="A142" t="s">
         <v>290</v>
       </c>
-      <c r="B142" s="3" t="s">
+      <c r="B142" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="C142" s="4" t="s">
+      <c r="C142" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D142" s="1" t="s">
@@ -4792,10 +4805,10 @@
       <c r="A143" t="s">
         <v>292</v>
       </c>
-      <c r="B143" s="3" t="s">
+      <c r="B143" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="C143" s="4" t="s">
+      <c r="C143" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D143" s="1" t="s">
@@ -4812,10 +4825,10 @@
       <c r="A144" t="s">
         <v>294</v>
       </c>
-      <c r="B144" s="3" t="s">
+      <c r="B144" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C144" s="4" t="s">
+      <c r="C144" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D144" s="1" t="s">
@@ -4832,10 +4845,10 @@
       <c r="A145" t="s">
         <v>296</v>
       </c>
-      <c r="B145" s="3" t="s">
+      <c r="B145" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="C145" s="4" t="s">
+      <c r="C145" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D145" s="1" t="s">
@@ -4852,10 +4865,10 @@
       <c r="A146" t="s">
         <v>298</v>
       </c>
-      <c r="B146" s="3" t="s">
+      <c r="B146" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="C146" s="4" t="s">
+      <c r="C146" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D146" s="1" t="s">
@@ -4870,12 +4883,12 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" t="s">
+        <v>280</v>
+      </c>
+      <c r="B147" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="B147" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="C147" s="4" t="s">
+      <c r="C147" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D147" s="1" t="s">
@@ -4890,12 +4903,12 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" t="s">
+        <v>301</v>
+      </c>
+      <c r="B148" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="B148" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="C148" s="4" t="s">
+      <c r="C148" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D148" s="1" t="s">
@@ -4910,12 +4923,12 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" t="s">
+        <v>303</v>
+      </c>
+      <c r="B149" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="B149" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="C149" s="4" t="s">
+      <c r="C149" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D149" s="1" t="s">
@@ -4930,12 +4943,12 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
+        <v>305</v>
+      </c>
+      <c r="B150" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="B150" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="C150" s="4" t="s">
+      <c r="C150" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D150" s="1" t="s">
@@ -4950,12 +4963,12 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" t="s">
+        <v>307</v>
+      </c>
+      <c r="B151" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="B151" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="C151" s="4" t="s">
+      <c r="C151" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D151" s="1" t="s">
@@ -4970,13 +4983,13 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>310</v>
-      </c>
-      <c r="B152" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="C152" s="4">
-        <v>3</v>
+        <v>309</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>9</v>
@@ -4990,13 +5003,13 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>312</v>
-      </c>
-      <c r="B153" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C153" s="4">
-        <v>3</v>
+        <v>310</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>9</v>
@@ -5010,30 +5023,277 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" t="s">
+        <v>311</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E154" t="s">
+        <v>10</v>
+      </c>
+      <c r="F154" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155" t="s">
+        <v>312</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E155" t="s">
+        <v>10</v>
+      </c>
+      <c r="F155" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="A156" t="s">
+        <v>313</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E156" t="s">
+        <v>10</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="A157" t="s">
         <v>314</v>
       </c>
-      <c r="B154" s="3" t="s">
+      <c r="B157" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E157" t="s">
+        <v>10</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
+      <c r="A158" t="s">
         <v>315</v>
       </c>
-      <c r="C154" s="4">
-        <v>3</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E154" t="s">
-        <v>10</v>
-      </c>
-      <c r="F154" s="1" t="s">
+      <c r="B158" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E158" t="s">
+        <v>10</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159" t="s">
+        <v>316</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E159" t="s">
+        <v>10</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
+      <c r="A160" t="s">
+        <v>317</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E160" t="s">
+        <v>10</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="A161" t="s">
+        <v>318</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E161" t="s">
+        <v>10</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="A162" t="s">
+        <v>319</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E162" t="s">
+        <v>10</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="A163" t="s">
+        <v>320</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E163" t="s">
+        <v>10</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="A164" t="s">
+        <v>321</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E164" t="s">
+        <v>10</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="A165" t="s">
+        <v>322</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E165" t="s">
+        <v>10</v>
+      </c>
+      <c r="F165" s="1" t="s">
         <v>11</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F153" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
-  <conditionalFormatting sqref="B$1:B$1048576">
+  <conditionalFormatting sqref="B138">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B148">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A149">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B149">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A150">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B150">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A151">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B151">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B152:B165">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B137 B139:B147 B166:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
